--- a/experiments/forecasting/forecasting_DLinear.xlsx
+++ b/experiments/forecasting/forecasting_DLinear.xlsx
@@ -13,11 +13,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ndUPC_DLinear" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="mUPC_DLinear" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rUPC_DLinear" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SPCP_DLinear" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="augmented_DLinear" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="r+r_DLinear" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="descriptive" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="per_seed_DLinear" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="noSPCP_DLinear" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SPCP_DLinear" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="augmented_DLinear" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="r+r_DLinear" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="descriptive" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="per_seed_DLinear" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,7 +568,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>synthetic (mUPC): noUPC + mapped UPC (= Ch.5 noSPCP)</t>
+          <t>synthetic (mUPC): noUPC + mapped UPC</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -615,7 +616,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SPCP_DLinear</t>
+          <t>noSPCP_DLinear</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -625,26 +626,26 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>synthetic (SPCP): VA-generated appliance PCPs</t>
+          <t>synthetic (noSPCP): Ch.5 baseline, copied real PCPs + mapped UPC (own simulation)</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.9349</v>
+        <v>0.9357</v>
       </c>
       <c r="E7" t="n">
-        <v>0.983</v>
+        <v>0.9769</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8062</v>
+        <v>0.8024</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9373</v>
+        <v>0.9332</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>augmented_DLinear</t>
+          <t>SPCP_DLinear</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -654,48 +655,77 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>augmented: noSPCP + SPCP</t>
+          <t>synthetic (SPCP): VA-generated appliance PCPs</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.9266</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9628</v>
+        <v>0.9674</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8001</v>
+        <v>0.7977</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9304</v>
+        <v>0.9327</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>augmented_DLinear</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>DLinear</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>augmented: noSPCP + SPCP</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.929</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.9563</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.7941</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.9323</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>r+r_DLinear</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>DLinear</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>r+r: real duplicated (data-volume control)</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D10" t="n">
         <v>0.9388</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E10" t="n">
         <v>0.9724</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F10" t="n">
         <v>0.7961</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G10" t="n">
         <v>0.9262</v>
       </c>
     </row>
@@ -710,605 +740,320 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>model</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>condition</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>metric</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>mean</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>rel%_vs_real</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>CI95_lo</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>CI95_hi</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>better/N</t>
+          <t>Konfig:</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DLinear</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>real</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>MASE</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>0.9431</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>experiment: r+r_DLinear</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DLinear</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>real</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>RMSSE</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>0.8005</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>model: DLinear</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DLinear</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>noUPC</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>MASE</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>0.9216</v>
-      </c>
-      <c r="E4" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="F4" t="n">
-        <v>-5</v>
-      </c>
-      <c r="G4" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>6/10</t>
+          <t>training data: r+r: real duplicated (data-volume control)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DLinear</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>noUPC</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>RMSSE</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>0.8084</v>
-      </c>
-      <c r="E5" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="F5" t="n">
-        <v>-5.9</v>
-      </c>
-      <c r="G5" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>4/10</t>
+          <t>input_chunk=192 output_chunk=96 epochs=50 batch=32 season(m)=96</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DLinear</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>ndUPC</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>MASE</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>0.8866000000000001</v>
-      </c>
-      <c r="E6" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="F6" t="n">
-        <v>-3.3</v>
-      </c>
-      <c r="G6" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>5/10</t>
+          <t>aggregate: meter1+2+3 (3-phase mains), 15min mean</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DLinear</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>ndUPC</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>RMSSE</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>0.791</v>
-      </c>
-      <c r="E7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="F7" t="n">
-        <v>-4.8</v>
-      </c>
-      <c r="G7" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>4/10</t>
+          <t>metrics: MASE (MAE-based) and RMSSE (RMSE-based), both scaled by seasonal-naive</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DLinear</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>mUPC</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>MASE</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>0.9441000000000001</v>
-      </c>
-      <c r="E8" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="F8" t="n">
-        <v>-1.1</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>2/10</t>
+          <t>transfer: train -&gt; test on real UNSEEN households</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DLinear</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>mUPC</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>RMSSE</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>0.8043</v>
-      </c>
-      <c r="E9" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="F9" t="n">
-        <v>-1</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>3/10</t>
+          <t>seeds: 10 (per-household value averaged over seeds)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DLinear</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>rUPC</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>MASE</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>0.9479</v>
-      </c>
-      <c r="E10" t="n">
-        <v>-0.7</v>
-      </c>
-      <c r="F10" t="n">
-        <v>-3.2</v>
-      </c>
-      <c r="G10" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>3/10</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>DLinear</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>rUPC</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>RMSSE</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>0.8008</v>
-      </c>
-      <c r="E11" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="F11" t="n">
-        <v>-2.2</v>
-      </c>
-      <c r="G11" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>6/10</t>
+          <t>test households (n=10): ['building11', 'building13', 'building17', 'building19', 'building20', 'building3', 'building5', 'building6', 'building8', 'building9']</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>DLinear</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>SPCP</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>MASE</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>0.9349</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F12" t="n">
-        <v>-4.1</v>
-      </c>
-      <c r="G12" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>5/10</t>
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>household</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t>MASE_mean</t>
+        </is>
+      </c>
+      <c r="C12" s="1" t="inlineStr">
+        <is>
+          <t>MASE_std</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="inlineStr">
+        <is>
+          <t>RMSSE_mean</t>
+        </is>
+      </c>
+      <c r="E12" s="1" t="inlineStr">
+        <is>
+          <t>RMSSE_std</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DLinear</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>SPCP</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>RMSSE</t>
-        </is>
+          <t>building11</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.4197</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.021</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8062</v>
+        <v>0.2891</v>
       </c>
       <c r="E13" t="n">
-        <v>-1</v>
-      </c>
-      <c r="F13" t="n">
-        <v>-5.3</v>
-      </c>
-      <c r="G13" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>3/10</t>
-        </is>
+        <v>0.0095</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DLinear</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>augmented</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>MASE</t>
-        </is>
+          <t>building13</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1.0874</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.024</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9330000000000001</v>
+        <v>1.0686</v>
       </c>
       <c r="E14" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="F14" t="n">
-        <v>-1.6</v>
-      </c>
-      <c r="G14" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>7/10</t>
-        </is>
+        <v>0.015</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DLinear</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>augmented</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>RMSSE</t>
-        </is>
+          <t>building17</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.9426</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.0485</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8001</v>
+        <v>0.5715</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="F15" t="n">
-        <v>-1.8</v>
-      </c>
-      <c r="G15" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>5/10</t>
-        </is>
+        <v>0.0259</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DLinear</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>r+r</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>MASE</t>
-        </is>
+          <t>building19</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1.011</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.0321</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9388</v>
+        <v>0.9552</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F16" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="G16" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>6/10</t>
-        </is>
+        <v>0.0227</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>DLinear</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>r+r</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>RMSSE</t>
-        </is>
+          <t>building20</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1.2405</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.0396</v>
       </c>
       <c r="D17" t="n">
+        <v>1.0521</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.0189</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>building3</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0.4471</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.0144</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.4847</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.0046</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>building5</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1.5666</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.0555</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1.1016</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.0202</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>building6</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0.9114</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.9496</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.0153</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>building8</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0.7592</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.0244</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.5854</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.0135</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>building9</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1.0021</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.0194</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.9028</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.0125</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>aggregate (mean over households)</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>0.9388</v>
+      </c>
+      <c r="D23" t="n">
         <v>0.7961</v>
       </c>
-      <c r="E17" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>1</v>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>8/10</t>
-        </is>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>aggregate (median over households)</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>0.9724</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.9262</v>
       </c>
     </row>
   </sheetData>
@@ -1322,12 +1067,692 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M209"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>condition</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>rel%_vs_real</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>CI95_lo</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>CI95_hi</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>better/N</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>DLinear</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>real</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>MASE</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.9431</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>DLinear</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>real</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>RMSSE</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0.8005</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>DLinear</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>noUPC</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>MASE</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.9216</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="G4" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>6/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>DLinear</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>noUPC</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>RMSSE</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0.8084</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-5.9</v>
+      </c>
+      <c r="G5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>4/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>DLinear</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ndUPC</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>MASE</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.8866000000000001</v>
+      </c>
+      <c r="E6" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-3.3</v>
+      </c>
+      <c r="G6" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>5/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>DLinear</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ndUPC</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>RMSSE</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-4.8</v>
+      </c>
+      <c r="G7" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>4/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>DLinear</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>mUPC</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>MASE</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.9441000000000001</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>DLinear</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>mUPC</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>RMSSE</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.8043</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>3/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>DLinear</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>rUPC</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>MASE</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.9479</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-3.2</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>3/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>DLinear</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>rUPC</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>RMSSE</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0.8008</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>6/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>DLinear</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>noSPCP</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>MASE</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0.9357</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>5/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>DLinear</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>noSPCP</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>RMSSE</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0.8024</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>3/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>DLinear</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>SPCP</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>MASE</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0.9266</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="G14" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>7/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>DLinear</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>SPCP</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>RMSSE</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0.7977</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>5/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>DLinear</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>augmented</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>MASE</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0.929</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>7/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>DLinear</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>augmented</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>RMSSE</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0.7941</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>8/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>DLinear</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>r+r</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>MASE</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0.9388</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>6/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>DLinear</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>r+r</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>RMSSE</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0.7961</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>8/10</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M235"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
           <t>Per-seed values (DLinear) — rows: households; cols: seed0..seed9; MASE and RMSSE blocks per condition. Reconstructed from raw/*.npy.</t>
         </is>
       </c>
@@ -6375,7 +6800,7 @@
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>SPCP — MASE</t>
+          <t>noSPCP — MASE</t>
         </is>
       </c>
     </row>
@@ -6453,40 +6878,40 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.4546</v>
+        <v>0.374</v>
       </c>
       <c r="C135" t="n">
-        <v>0.449</v>
+        <v>0.445</v>
       </c>
       <c r="D135" t="n">
-        <v>0.4522</v>
+        <v>0.45</v>
       </c>
       <c r="E135" t="n">
-        <v>0.4704</v>
+        <v>0.4537</v>
       </c>
       <c r="F135" t="n">
-        <v>0.4521</v>
+        <v>0.4223</v>
       </c>
       <c r="G135" t="n">
-        <v>0.4656</v>
+        <v>0.4157</v>
       </c>
       <c r="H135" t="n">
-        <v>0.4896</v>
+        <v>0.4785</v>
       </c>
       <c r="I135" t="n">
-        <v>0.4414</v>
+        <v>0.4302</v>
       </c>
       <c r="J135" t="n">
-        <v>0.4613</v>
+        <v>0.4373</v>
       </c>
       <c r="K135" t="n">
-        <v>0.4874</v>
+        <v>0.4348</v>
       </c>
       <c r="L135" t="n">
-        <v>0.4623</v>
+        <v>0.4341</v>
       </c>
       <c r="M135" t="n">
-        <v>0.0161</v>
+        <v>0.0276</v>
       </c>
     </row>
     <row r="136">
@@ -6496,40 +6921,40 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>1.0522</v>
+        <v>1.0935</v>
       </c>
       <c r="C136" t="n">
-        <v>1.0421</v>
+        <v>1.1122</v>
       </c>
       <c r="D136" t="n">
-        <v>1.0126</v>
+        <v>1.0049</v>
       </c>
       <c r="E136" t="n">
-        <v>1.0614</v>
+        <v>1.0705</v>
       </c>
       <c r="F136" t="n">
-        <v>1.0274</v>
+        <v>1.1027</v>
       </c>
       <c r="G136" t="n">
-        <v>1.0364</v>
+        <v>1.1222</v>
       </c>
       <c r="H136" t="n">
-        <v>1.035</v>
+        <v>1.1445</v>
       </c>
       <c r="I136" t="n">
-        <v>1.0391</v>
+        <v>1.0712</v>
       </c>
       <c r="J136" t="n">
-        <v>0.9925</v>
+        <v>1.0805</v>
       </c>
       <c r="K136" t="n">
-        <v>1.0937</v>
+        <v>1.0843</v>
       </c>
       <c r="L136" t="n">
-        <v>1.0392</v>
+        <v>1.0887</v>
       </c>
       <c r="M136" t="n">
-        <v>0.0273</v>
+        <v>0.0376</v>
       </c>
     </row>
     <row r="137">
@@ -6539,40 +6964,40 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.8473000000000001</v>
+        <v>0.891</v>
       </c>
       <c r="C137" t="n">
-        <v>0.8585</v>
+        <v>0.8831</v>
       </c>
       <c r="D137" t="n">
-        <v>0.8125</v>
+        <v>0.8748</v>
       </c>
       <c r="E137" t="n">
-        <v>0.8119</v>
+        <v>0.8951</v>
       </c>
       <c r="F137" t="n">
-        <v>0.8051</v>
+        <v>0.9056</v>
       </c>
       <c r="G137" t="n">
-        <v>0.7454</v>
+        <v>0.9855</v>
       </c>
       <c r="H137" t="n">
-        <v>0.9587</v>
+        <v>0.928</v>
       </c>
       <c r="I137" t="n">
-        <v>0.8955</v>
+        <v>0.9146</v>
       </c>
       <c r="J137" t="n">
-        <v>0.8310999999999999</v>
+        <v>0.8551</v>
       </c>
       <c r="K137" t="n">
-        <v>0.9489</v>
+        <v>0.892</v>
       </c>
       <c r="L137" t="n">
-        <v>0.8515</v>
+        <v>0.9025</v>
       </c>
       <c r="M137" t="n">
-        <v>0.06660000000000001</v>
+        <v>0.0356</v>
       </c>
     </row>
     <row r="138">
@@ -6582,40 +7007,40 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>1.0229</v>
+        <v>1.004</v>
       </c>
       <c r="C138" t="n">
-        <v>0.9757</v>
+        <v>1.0054</v>
       </c>
       <c r="D138" t="n">
-        <v>1.0149</v>
+        <v>1.0292</v>
       </c>
       <c r="E138" t="n">
-        <v>1.0491</v>
+        <v>0.9874000000000001</v>
       </c>
       <c r="F138" t="n">
-        <v>1.0028</v>
+        <v>1.0402</v>
       </c>
       <c r="G138" t="n">
-        <v>1.0381</v>
+        <v>1.0191</v>
       </c>
       <c r="H138" t="n">
-        <v>1.0283</v>
+        <v>1.0413</v>
       </c>
       <c r="I138" t="n">
-        <v>1.0116</v>
+        <v>1.0161</v>
       </c>
       <c r="J138" t="n">
-        <v>1.0613</v>
+        <v>0.9899</v>
       </c>
       <c r="K138" t="n">
-        <v>1.0254</v>
+        <v>1.0114</v>
       </c>
       <c r="L138" t="n">
-        <v>1.023</v>
+        <v>1.0144</v>
       </c>
       <c r="M138" t="n">
-        <v>0.0242</v>
+        <v>0.0187</v>
       </c>
     </row>
     <row r="139">
@@ -6625,40 +7050,40 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>1.2533</v>
+        <v>1.1707</v>
       </c>
       <c r="C139" t="n">
-        <v>1.3005</v>
+        <v>1.2059</v>
       </c>
       <c r="D139" t="n">
-        <v>1.255</v>
+        <v>1.2321</v>
       </c>
       <c r="E139" t="n">
-        <v>1.2833</v>
+        <v>1.272</v>
       </c>
       <c r="F139" t="n">
-        <v>1.2476</v>
+        <v>1.227</v>
       </c>
       <c r="G139" t="n">
-        <v>1.2531</v>
+        <v>1.1734</v>
       </c>
       <c r="H139" t="n">
-        <v>1.2549</v>
+        <v>1.2461</v>
       </c>
       <c r="I139" t="n">
-        <v>1.1842</v>
+        <v>1.1789</v>
       </c>
       <c r="J139" t="n">
-        <v>1.2325</v>
+        <v>1.1548</v>
       </c>
       <c r="K139" t="n">
-        <v>1.2842</v>
+        <v>1.248</v>
       </c>
       <c r="L139" t="n">
-        <v>1.2549</v>
+        <v>1.2109</v>
       </c>
       <c r="M139" t="n">
-        <v>0.0322</v>
+        <v>0.0398</v>
       </c>
     </row>
     <row r="140">
@@ -6668,40 +7093,40 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.4727</v>
+        <v>0.4432</v>
       </c>
       <c r="C140" t="n">
-        <v>0.4844</v>
+        <v>0.4561</v>
       </c>
       <c r="D140" t="n">
-        <v>0.4884</v>
+        <v>0.4734</v>
       </c>
       <c r="E140" t="n">
-        <v>0.494</v>
+        <v>0.4725</v>
       </c>
       <c r="F140" t="n">
-        <v>0.4675</v>
+        <v>0.4345</v>
       </c>
       <c r="G140" t="n">
-        <v>0.4835</v>
+        <v>0.4412</v>
       </c>
       <c r="H140" t="n">
-        <v>0.5011</v>
+        <v>0.4587</v>
       </c>
       <c r="I140" t="n">
-        <v>0.439</v>
+        <v>0.4345</v>
       </c>
       <c r="J140" t="n">
-        <v>0.4775</v>
+        <v>0.4764</v>
       </c>
       <c r="K140" t="n">
-        <v>0.4942</v>
+        <v>0.4582</v>
       </c>
       <c r="L140" t="n">
-        <v>0.4802</v>
+        <v>0.4549</v>
       </c>
       <c r="M140" t="n">
-        <v>0.0178</v>
+        <v>0.016</v>
       </c>
     </row>
     <row r="141">
@@ -6711,40 +7136,40 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>1.5553</v>
+        <v>1.4245</v>
       </c>
       <c r="C141" t="n">
-        <v>1.5985</v>
+        <v>1.6169</v>
       </c>
       <c r="D141" t="n">
-        <v>1.6089</v>
+        <v>1.6025</v>
       </c>
       <c r="E141" t="n">
-        <v>1.6111</v>
+        <v>1.6648</v>
       </c>
       <c r="F141" t="n">
-        <v>1.5389</v>
+        <v>1.4583</v>
       </c>
       <c r="G141" t="n">
-        <v>1.5482</v>
+        <v>1.5037</v>
       </c>
       <c r="H141" t="n">
-        <v>1.6303</v>
+        <v>1.5568</v>
       </c>
       <c r="I141" t="n">
-        <v>1.5259</v>
+        <v>1.5292</v>
       </c>
       <c r="J141" t="n">
-        <v>1.5828</v>
+        <v>1.528</v>
       </c>
       <c r="K141" t="n">
-        <v>1.5839</v>
+        <v>1.5714</v>
       </c>
       <c r="L141" t="n">
-        <v>1.5784</v>
+        <v>1.5456</v>
       </c>
       <c r="M141" t="n">
-        <v>0.0348</v>
+        <v>0.073</v>
       </c>
     </row>
     <row r="142">
@@ -6754,40 +7179,40 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.95</v>
+        <v>0.9206</v>
       </c>
       <c r="C142" t="n">
-        <v>0.9507</v>
+        <v>0.9500999999999999</v>
       </c>
       <c r="D142" t="n">
-        <v>0.9389999999999999</v>
+        <v>0.9532</v>
       </c>
       <c r="E142" t="n">
-        <v>0.987</v>
+        <v>0.9231</v>
       </c>
       <c r="F142" t="n">
-        <v>0.9675</v>
+        <v>0.9315</v>
       </c>
       <c r="G142" t="n">
-        <v>0.9651999999999999</v>
+        <v>0.9633</v>
       </c>
       <c r="H142" t="n">
-        <v>0.9540999999999999</v>
+        <v>0.9558</v>
       </c>
       <c r="I142" t="n">
-        <v>0.956</v>
+        <v>0.9535</v>
       </c>
       <c r="J142" t="n">
-        <v>1.0021</v>
+        <v>0.9364</v>
       </c>
       <c r="K142" t="n">
-        <v>0.9267</v>
+        <v>0.9404</v>
       </c>
       <c r="L142" t="n">
-        <v>0.9598</v>
+        <v>0.9428</v>
       </c>
       <c r="M142" t="n">
-        <v>0.022</v>
+        <v>0.0146</v>
       </c>
     </row>
     <row r="143">
@@ -6797,40 +7222,40 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.6564</v>
+        <v>0.7246</v>
       </c>
       <c r="C143" t="n">
-        <v>0.7277</v>
+        <v>0.7837</v>
       </c>
       <c r="D143" t="n">
-        <v>0.6582</v>
+        <v>0.7599</v>
       </c>
       <c r="E143" t="n">
-        <v>0.6354</v>
+        <v>0.7397</v>
       </c>
       <c r="F143" t="n">
-        <v>0.6925</v>
+        <v>0.7169</v>
       </c>
       <c r="G143" t="n">
-        <v>0.6938</v>
+        <v>0.7796</v>
       </c>
       <c r="H143" t="n">
-        <v>0.7772</v>
+        <v>0.8653</v>
       </c>
       <c r="I143" t="n">
-        <v>0.6699000000000001</v>
+        <v>0.7484</v>
       </c>
       <c r="J143" t="n">
-        <v>0.6133999999999999</v>
+        <v>0.6649</v>
       </c>
       <c r="K143" t="n">
-        <v>0.8058</v>
+        <v>0.7406</v>
       </c>
       <c r="L143" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.7523</v>
       </c>
       <c r="M143" t="n">
-        <v>0.0613</v>
+        <v>0.0522</v>
       </c>
     </row>
     <row r="144">
@@ -6840,46 +7265,46 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.9933</v>
+        <v>1.0848</v>
       </c>
       <c r="C144" t="n">
-        <v>0.9462</v>
+        <v>1.0089</v>
       </c>
       <c r="D144" t="n">
-        <v>0.9933999999999999</v>
+        <v>0.9879</v>
       </c>
       <c r="E144" t="n">
-        <v>1.0585</v>
+        <v>1.0062</v>
       </c>
       <c r="F144" t="n">
-        <v>1.0248</v>
+        <v>0.9703000000000001</v>
       </c>
       <c r="G144" t="n">
-        <v>1.0097</v>
+        <v>0.9832</v>
       </c>
       <c r="H144" t="n">
-        <v>0.966</v>
+        <v>0.9946</v>
       </c>
       <c r="I144" t="n">
-        <v>1.0282</v>
+        <v>1.0004</v>
       </c>
       <c r="J144" t="n">
-        <v>1.0183</v>
+        <v>1.0779</v>
       </c>
       <c r="K144" t="n">
-        <v>1.0236</v>
+        <v>0.9955000000000001</v>
       </c>
       <c r="L144" t="n">
-        <v>1.0062</v>
+        <v>1.011</v>
       </c>
       <c r="M144" t="n">
-        <v>0.0326</v>
+        <v>0.0388</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>SPCP — RMSSE</t>
+          <t>noSPCP — RMSSE</t>
         </is>
       </c>
     </row>
@@ -6957,40 +7382,40 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.3307</v>
+        <v>0.2777</v>
       </c>
       <c r="C148" t="n">
-        <v>0.3223</v>
+        <v>0.3056</v>
       </c>
       <c r="D148" t="n">
-        <v>0.3364</v>
+        <v>0.3057</v>
       </c>
       <c r="E148" t="n">
-        <v>0.3326</v>
+        <v>0.3169</v>
       </c>
       <c r="F148" t="n">
-        <v>0.3256</v>
+        <v>0.2873</v>
       </c>
       <c r="G148" t="n">
-        <v>0.3329</v>
+        <v>0.2824</v>
       </c>
       <c r="H148" t="n">
-        <v>0.3473</v>
+        <v>0.3099</v>
       </c>
       <c r="I148" t="n">
-        <v>0.309</v>
+        <v>0.291</v>
       </c>
       <c r="J148" t="n">
-        <v>0.3259</v>
+        <v>0.2998</v>
       </c>
       <c r="K148" t="n">
-        <v>0.3358</v>
+        <v>0.2958</v>
       </c>
       <c r="L148" t="n">
-        <v>0.3298</v>
+        <v>0.2972</v>
       </c>
       <c r="M148" t="n">
-        <v>0.0101</v>
+        <v>0.0126</v>
       </c>
     </row>
     <row r="149">
@@ -7000,40 +7425,40 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>1.0769</v>
+        <v>1.116</v>
       </c>
       <c r="C149" t="n">
-        <v>1.0499</v>
+        <v>1.0949</v>
       </c>
       <c r="D149" t="n">
-        <v>1.0632</v>
+        <v>1.0646</v>
       </c>
       <c r="E149" t="n">
-        <v>1.0747</v>
+        <v>1.065</v>
       </c>
       <c r="F149" t="n">
-        <v>1.0477</v>
+        <v>1.084</v>
       </c>
       <c r="G149" t="n">
-        <v>1.0656</v>
+        <v>1.0899</v>
       </c>
       <c r="H149" t="n">
-        <v>1.0431</v>
+        <v>1.1001</v>
       </c>
       <c r="I149" t="n">
-        <v>1.06</v>
+        <v>1.0777</v>
       </c>
       <c r="J149" t="n">
-        <v>1.0584</v>
+        <v>1.0866</v>
       </c>
       <c r="K149" t="n">
-        <v>1.0499</v>
+        <v>1.0795</v>
       </c>
       <c r="L149" t="n">
-        <v>1.0589</v>
+        <v>1.0858</v>
       </c>
       <c r="M149" t="n">
-        <v>0.0114</v>
+        <v>0.0157</v>
       </c>
     </row>
     <row r="150">
@@ -7043,40 +7468,40 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.5251</v>
+        <v>0.5711000000000001</v>
       </c>
       <c r="C150" t="n">
-        <v>0.5167</v>
+        <v>0.5392</v>
       </c>
       <c r="D150" t="n">
-        <v>0.494</v>
+        <v>0.5557</v>
       </c>
       <c r="E150" t="n">
-        <v>0.5024999999999999</v>
+        <v>0.5458</v>
       </c>
       <c r="F150" t="n">
-        <v>0.4946</v>
+        <v>0.5644</v>
       </c>
       <c r="G150" t="n">
-        <v>0.4814</v>
+        <v>0.6046</v>
       </c>
       <c r="H150" t="n">
-        <v>0.5614</v>
+        <v>0.5691000000000001</v>
       </c>
       <c r="I150" t="n">
-        <v>0.5364</v>
+        <v>0.5451</v>
       </c>
       <c r="J150" t="n">
-        <v>0.5098</v>
+        <v>0.5397</v>
       </c>
       <c r="K150" t="n">
-        <v>0.5713</v>
+        <v>0.5377</v>
       </c>
       <c r="L150" t="n">
-        <v>0.5193</v>
+        <v>0.5572</v>
       </c>
       <c r="M150" t="n">
-        <v>0.0296</v>
+        <v>0.0209</v>
       </c>
     </row>
     <row r="151">
@@ -7086,40 +7511,40 @@
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.965</v>
+        <v>0.9577</v>
       </c>
       <c r="C151" t="n">
-        <v>0.9491000000000001</v>
+        <v>0.9606</v>
       </c>
       <c r="D151" t="n">
-        <v>0.9624</v>
+        <v>0.9804</v>
       </c>
       <c r="E151" t="n">
-        <v>0.9953</v>
+        <v>0.9494</v>
       </c>
       <c r="F151" t="n">
-        <v>0.9769</v>
+        <v>0.992</v>
       </c>
       <c r="G151" t="n">
-        <v>0.9622000000000001</v>
+        <v>0.9559</v>
       </c>
       <c r="H151" t="n">
-        <v>0.9606</v>
+        <v>0.951</v>
       </c>
       <c r="I151" t="n">
-        <v>0.96</v>
+        <v>0.9704</v>
       </c>
       <c r="J151" t="n">
-        <v>1.0069</v>
+        <v>0.9684</v>
       </c>
       <c r="K151" t="n">
-        <v>0.9271</v>
+        <v>0.9669</v>
       </c>
       <c r="L151" t="n">
-        <v>0.9666</v>
+        <v>0.9653</v>
       </c>
       <c r="M151" t="n">
-        <v>0.0225</v>
+        <v>0.0134</v>
       </c>
     </row>
     <row r="152">
@@ -7129,40 +7554,40 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>1.1051</v>
+        <v>1.0307</v>
       </c>
       <c r="C152" t="n">
-        <v>1.1598</v>
+        <v>1.0706</v>
       </c>
       <c r="D152" t="n">
-        <v>1.1656</v>
+        <v>1.1086</v>
       </c>
       <c r="E152" t="n">
-        <v>1.1498</v>
+        <v>1.1223</v>
       </c>
       <c r="F152" t="n">
-        <v>1.1072</v>
+        <v>1.0868</v>
       </c>
       <c r="G152" t="n">
-        <v>1.1095</v>
+        <v>1.0299</v>
       </c>
       <c r="H152" t="n">
-        <v>1.1034</v>
+        <v>1.0813</v>
       </c>
       <c r="I152" t="n">
-        <v>1.066</v>
+        <v>1.0375</v>
       </c>
       <c r="J152" t="n">
-        <v>1.1117</v>
+        <v>1.0587</v>
       </c>
       <c r="K152" t="n">
-        <v>1.0735</v>
+        <v>1.093</v>
       </c>
       <c r="L152" t="n">
-        <v>1.1152</v>
+        <v>1.0719</v>
       </c>
       <c r="M152" t="n">
-        <v>0.0337</v>
+        <v>0.0324</v>
       </c>
     </row>
     <row r="153">
@@ -7172,40 +7597,40 @@
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.4895</v>
+        <v>0.4789</v>
       </c>
       <c r="C153" t="n">
-        <v>0.508</v>
+        <v>0.4959</v>
       </c>
       <c r="D153" t="n">
-        <v>0.5181</v>
+        <v>0.5065</v>
       </c>
       <c r="E153" t="n">
-        <v>0.5084</v>
+        <v>0.5019</v>
       </c>
       <c r="F153" t="n">
-        <v>0.496</v>
+        <v>0.4908</v>
       </c>
       <c r="G153" t="n">
-        <v>0.4924</v>
+        <v>0.4814</v>
       </c>
       <c r="H153" t="n">
-        <v>0.5078</v>
+        <v>0.4864</v>
       </c>
       <c r="I153" t="n">
-        <v>0.4764</v>
+        <v>0.4806</v>
       </c>
       <c r="J153" t="n">
-        <v>0.5012</v>
+        <v>0.4996</v>
       </c>
       <c r="K153" t="n">
-        <v>0.4964</v>
+        <v>0.4932</v>
       </c>
       <c r="L153" t="n">
-        <v>0.4994</v>
+        <v>0.4915</v>
       </c>
       <c r="M153" t="n">
-        <v>0.0119</v>
+        <v>0.009599999999999999</v>
       </c>
     </row>
     <row r="154">
@@ -7215,40 +7640,40 @@
         </is>
       </c>
       <c r="B154" t="n">
-        <v>1.1208</v>
+        <v>1.0211</v>
       </c>
       <c r="C154" t="n">
-        <v>1.1213</v>
+        <v>1.1142</v>
       </c>
       <c r="D154" t="n">
-        <v>1.1228</v>
+        <v>1.1011</v>
       </c>
       <c r="E154" t="n">
-        <v>1.1431</v>
+        <v>1.1522</v>
       </c>
       <c r="F154" t="n">
-        <v>1.1206</v>
+        <v>1.0613</v>
       </c>
       <c r="G154" t="n">
-        <v>1.1016</v>
+        <v>1.0657</v>
       </c>
       <c r="H154" t="n">
-        <v>1.1091</v>
+        <v>1.0808</v>
       </c>
       <c r="I154" t="n">
-        <v>1.0918</v>
+        <v>1.0911</v>
       </c>
       <c r="J154" t="n">
-        <v>1.1325</v>
+        <v>1.0993</v>
       </c>
       <c r="K154" t="n">
-        <v>1.1026</v>
+        <v>1.114</v>
       </c>
       <c r="L154" t="n">
-        <v>1.1166</v>
+        <v>1.0901</v>
       </c>
       <c r="M154" t="n">
-        <v>0.0154</v>
+        <v>0.0357</v>
       </c>
     </row>
     <row r="155">
@@ -7258,40 +7683,40 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.995</v>
+        <v>0.9772999999999999</v>
       </c>
       <c r="C155" t="n">
-        <v>0.9752</v>
+        <v>0.9677</v>
       </c>
       <c r="D155" t="n">
-        <v>0.9965000000000001</v>
+        <v>0.9762</v>
       </c>
       <c r="E155" t="n">
-        <v>1.0062</v>
+        <v>0.9663</v>
       </c>
       <c r="F155" t="n">
-        <v>1.0085</v>
+        <v>0.9578</v>
       </c>
       <c r="G155" t="n">
-        <v>0.999</v>
+        <v>0.9887</v>
       </c>
       <c r="H155" t="n">
-        <v>0.9938</v>
+        <v>0.9482</v>
       </c>
       <c r="I155" t="n">
-        <v>1.0036</v>
+        <v>0.9837</v>
       </c>
       <c r="J155" t="n">
-        <v>1.0077</v>
+        <v>0.975</v>
       </c>
       <c r="K155" t="n">
-        <v>0.9476</v>
+        <v>0.9689</v>
       </c>
       <c r="L155" t="n">
-        <v>0.9933</v>
+        <v>0.971</v>
       </c>
       <c r="M155" t="n">
-        <v>0.0188</v>
+        <v>0.012</v>
       </c>
     </row>
     <row r="156">
@@ -7301,40 +7726,40 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.5427999999999999</v>
+        <v>0.6092</v>
       </c>
       <c r="C156" t="n">
-        <v>0.5686</v>
+        <v>0.6122</v>
       </c>
       <c r="D156" t="n">
-        <v>0.5506</v>
+        <v>0.6049</v>
       </c>
       <c r="E156" t="n">
-        <v>0.5273</v>
+        <v>0.592</v>
       </c>
       <c r="F156" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.5709</v>
       </c>
       <c r="G156" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.5972</v>
       </c>
       <c r="H156" t="n">
-        <v>0.583</v>
+        <v>0.6233</v>
       </c>
       <c r="I156" t="n">
-        <v>0.5336</v>
+        <v>0.5782</v>
       </c>
       <c r="J156" t="n">
-        <v>0.5238</v>
+        <v>0.5541</v>
       </c>
       <c r="K156" t="n">
-        <v>0.5931999999999999</v>
+        <v>0.5839</v>
       </c>
       <c r="L156" t="n">
-        <v>0.5548999999999999</v>
+        <v>0.5926</v>
       </c>
       <c r="M156" t="n">
-        <v>0.0234</v>
+        <v>0.0211</v>
       </c>
     </row>
     <row r="157">
@@ -7344,46 +7769,46 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>0.9036</v>
+        <v>0.931</v>
       </c>
       <c r="C157" t="n">
-        <v>0.8905999999999999</v>
+        <v>0.9052</v>
       </c>
       <c r="D157" t="n">
-        <v>0.9207</v>
+        <v>0.8829</v>
       </c>
       <c r="E157" t="n">
-        <v>0.9154</v>
+        <v>0.8782</v>
       </c>
       <c r="F157" t="n">
-        <v>0.9187</v>
+        <v>0.8787</v>
       </c>
       <c r="G157" t="n">
-        <v>0.9</v>
+        <v>0.9173</v>
       </c>
       <c r="H157" t="n">
-        <v>0.8962</v>
+        <v>0.8869</v>
       </c>
       <c r="I157" t="n">
-        <v>0.9113</v>
+        <v>0.8983</v>
       </c>
       <c r="J157" t="n">
-        <v>0.9175</v>
+        <v>0.9344</v>
       </c>
       <c r="K157" t="n">
-        <v>0.9056999999999999</v>
+        <v>0.8985</v>
       </c>
       <c r="L157" t="n">
-        <v>0.908</v>
+        <v>0.9011</v>
       </c>
       <c r="M157" t="n">
-        <v>0.0103</v>
+        <v>0.0207</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="inlineStr">
         <is>
-          <t>augmented — MASE</t>
+          <t>SPCP — MASE</t>
         </is>
       </c>
     </row>
@@ -7461,40 +7886,40 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>0.4295</v>
+        <v>0.3944</v>
       </c>
       <c r="C161" t="n">
-        <v>0.484</v>
+        <v>0.4492</v>
       </c>
       <c r="D161" t="n">
-        <v>0.4607</v>
+        <v>0.4476</v>
       </c>
       <c r="E161" t="n">
-        <v>0.4896</v>
+        <v>0.4469</v>
       </c>
       <c r="F161" t="n">
-        <v>0.427</v>
+        <v>0.4185</v>
       </c>
       <c r="G161" t="n">
-        <v>0.4341</v>
+        <v>0.412</v>
       </c>
       <c r="H161" t="n">
-        <v>0.4462</v>
+        <v>0.5004999999999999</v>
       </c>
       <c r="I161" t="n">
-        <v>0.4602</v>
+        <v>0.4357</v>
       </c>
       <c r="J161" t="n">
-        <v>0.4536</v>
+        <v>0.4395</v>
       </c>
       <c r="K161" t="n">
-        <v>0.4231</v>
+        <v>0.4449</v>
       </c>
       <c r="L161" t="n">
-        <v>0.4508</v>
+        <v>0.4389</v>
       </c>
       <c r="M161" t="n">
-        <v>0.0233</v>
+        <v>0.0283</v>
       </c>
     </row>
     <row r="162">
@@ -7504,40 +7929,40 @@
         </is>
       </c>
       <c r="B162" t="n">
-        <v>1.0318</v>
+        <v>1.063</v>
       </c>
       <c r="C162" t="n">
-        <v>1.0142</v>
+        <v>1.0652</v>
       </c>
       <c r="D162" t="n">
-        <v>1.0649</v>
+        <v>0.9816</v>
       </c>
       <c r="E162" t="n">
-        <v>1.0996</v>
+        <v>1.0365</v>
       </c>
       <c r="F162" t="n">
-        <v>1.042</v>
+        <v>1.0462</v>
       </c>
       <c r="G162" t="n">
-        <v>1.0458</v>
+        <v>1.0618</v>
       </c>
       <c r="H162" t="n">
-        <v>1.0508</v>
+        <v>1.1022</v>
       </c>
       <c r="I162" t="n">
-        <v>1.0614</v>
+        <v>1.0438</v>
       </c>
       <c r="J162" t="n">
-        <v>1.0846</v>
+        <v>1.0236</v>
       </c>
       <c r="K162" t="n">
-        <v>1.0379</v>
+        <v>1.0556</v>
       </c>
       <c r="L162" t="n">
-        <v>1.0533</v>
+        <v>1.048</v>
       </c>
       <c r="M162" t="n">
-        <v>0.0253</v>
+        <v>0.0314</v>
       </c>
     </row>
     <row r="163">
@@ -7547,40 +7972,40 @@
         </is>
       </c>
       <c r="B163" t="n">
-        <v>0.9246</v>
+        <v>0.9071</v>
       </c>
       <c r="C163" t="n">
-        <v>0.8921</v>
+        <v>0.8959</v>
       </c>
       <c r="D163" t="n">
-        <v>0.8577</v>
+        <v>0.8581</v>
       </c>
       <c r="E163" t="n">
-        <v>0.9083</v>
+        <v>0.8959</v>
       </c>
       <c r="F163" t="n">
-        <v>0.8791</v>
+        <v>0.9318</v>
       </c>
       <c r="G163" t="n">
-        <v>0.8359</v>
+        <v>0.9964</v>
       </c>
       <c r="H163" t="n">
-        <v>0.9014</v>
+        <v>0.9351</v>
       </c>
       <c r="I163" t="n">
-        <v>0.86</v>
+        <v>0.8914</v>
       </c>
       <c r="J163" t="n">
-        <v>0.8821</v>
+        <v>0.8352000000000001</v>
       </c>
       <c r="K163" t="n">
-        <v>0.8203</v>
+        <v>0.9621</v>
       </c>
       <c r="L163" t="n">
-        <v>0.8762</v>
+        <v>0.9109</v>
       </c>
       <c r="M163" t="n">
-        <v>0.0328</v>
+        <v>0.0475</v>
       </c>
     </row>
     <row r="164">
@@ -7590,40 +8015,40 @@
         </is>
       </c>
       <c r="B164" t="n">
-        <v>0.9814000000000001</v>
+        <v>0.9977</v>
       </c>
       <c r="C164" t="n">
-        <v>1.0408</v>
+        <v>1.0001</v>
       </c>
       <c r="D164" t="n">
-        <v>0.9866</v>
+        <v>1.0273</v>
       </c>
       <c r="E164" t="n">
-        <v>1.0183</v>
+        <v>1.0012</v>
       </c>
       <c r="F164" t="n">
-        <v>1.0201</v>
+        <v>1.0215</v>
       </c>
       <c r="G164" t="n">
-        <v>0.9734</v>
+        <v>1.0121</v>
       </c>
       <c r="H164" t="n">
-        <v>0.9825</v>
+        <v>1.052</v>
       </c>
       <c r="I164" t="n">
-        <v>1.0062</v>
+        <v>0.9998</v>
       </c>
       <c r="J164" t="n">
-        <v>0.9863</v>
+        <v>0.9895</v>
       </c>
       <c r="K164" t="n">
-        <v>1.0406</v>
+        <v>1.0227</v>
       </c>
       <c r="L164" t="n">
-        <v>1.0036</v>
+        <v>1.0124</v>
       </c>
       <c r="M164" t="n">
-        <v>0.0251</v>
+        <v>0.0187</v>
       </c>
     </row>
     <row r="165">
@@ -7633,40 +8058,40 @@
         </is>
       </c>
       <c r="B165" t="n">
-        <v>1.241</v>
+        <v>1.1915</v>
       </c>
       <c r="C165" t="n">
-        <v>1.2471</v>
+        <v>1.2304</v>
       </c>
       <c r="D165" t="n">
-        <v>1.2485</v>
+        <v>1.255</v>
       </c>
       <c r="E165" t="n">
-        <v>1.3131</v>
+        <v>1.299</v>
       </c>
       <c r="F165" t="n">
-        <v>1.2093</v>
+        <v>1.2571</v>
       </c>
       <c r="G165" t="n">
-        <v>1.2311</v>
+        <v>1.2036</v>
       </c>
       <c r="H165" t="n">
-        <v>1.2558</v>
+        <v>1.2933</v>
       </c>
       <c r="I165" t="n">
-        <v>1.2857</v>
+        <v>1.1727</v>
       </c>
       <c r="J165" t="n">
-        <v>1.2091</v>
+        <v>1.1945</v>
       </c>
       <c r="K165" t="n">
-        <v>1.2019</v>
+        <v>1.2695</v>
       </c>
       <c r="L165" t="n">
-        <v>1.2443</v>
+        <v>1.2367</v>
       </c>
       <c r="M165" t="n">
-        <v>0.035</v>
+        <v>0.0447</v>
       </c>
     </row>
     <row r="166">
@@ -7676,40 +8101,40 @@
         </is>
       </c>
       <c r="B166" t="n">
-        <v>0.4539</v>
+        <v>0.4484</v>
       </c>
       <c r="C166" t="n">
-        <v>0.4493</v>
+        <v>0.4546</v>
       </c>
       <c r="D166" t="n">
-        <v>0.4395</v>
+        <v>0.4739</v>
       </c>
       <c r="E166" t="n">
-        <v>0.4378</v>
+        <v>0.4622</v>
       </c>
       <c r="F166" t="n">
-        <v>0.4458</v>
+        <v>0.4459</v>
       </c>
       <c r="G166" t="n">
-        <v>0.4549</v>
+        <v>0.4509</v>
       </c>
       <c r="H166" t="n">
-        <v>0.4474</v>
+        <v>0.4659</v>
       </c>
       <c r="I166" t="n">
-        <v>0.4693</v>
+        <v>0.4548</v>
       </c>
       <c r="J166" t="n">
-        <v>0.4514</v>
+        <v>0.4858</v>
       </c>
       <c r="K166" t="n">
-        <v>0.4417</v>
+        <v>0.4675</v>
       </c>
       <c r="L166" t="n">
-        <v>0.4491</v>
+        <v>0.461</v>
       </c>
       <c r="M166" t="n">
-        <v>0.0092</v>
+        <v>0.0126</v>
       </c>
     </row>
     <row r="167">
@@ -7719,40 +8144,40 @@
         </is>
       </c>
       <c r="B167" t="n">
-        <v>1.5369</v>
+        <v>1.3866</v>
       </c>
       <c r="C167" t="n">
-        <v>1.6884</v>
+        <v>1.5722</v>
       </c>
       <c r="D167" t="n">
-        <v>1.576</v>
+        <v>1.505</v>
       </c>
       <c r="E167" t="n">
-        <v>1.6188</v>
+        <v>1.5402</v>
       </c>
       <c r="F167" t="n">
-        <v>1.5206</v>
+        <v>1.4205</v>
       </c>
       <c r="G167" t="n">
-        <v>1.5185</v>
+        <v>1.43</v>
       </c>
       <c r="H167" t="n">
-        <v>1.6107</v>
+        <v>1.5196</v>
       </c>
       <c r="I167" t="n">
-        <v>1.6229</v>
+        <v>1.5062</v>
       </c>
       <c r="J167" t="n">
-        <v>1.6737</v>
+        <v>1.5032</v>
       </c>
       <c r="K167" t="n">
-        <v>1.5567</v>
+        <v>1.5282</v>
       </c>
       <c r="L167" t="n">
-        <v>1.5923</v>
+        <v>1.4912</v>
       </c>
       <c r="M167" t="n">
-        <v>0.0606</v>
+        <v>0.0591</v>
       </c>
     </row>
     <row r="168">
@@ -7762,40 +8187,40 @@
         </is>
       </c>
       <c r="B168" t="n">
-        <v>0.9238</v>
+        <v>0.9028</v>
       </c>
       <c r="C168" t="n">
-        <v>0.9388</v>
+        <v>0.9348</v>
       </c>
       <c r="D168" t="n">
-        <v>0.9033</v>
+        <v>0.9261</v>
       </c>
       <c r="E168" t="n">
-        <v>0.8963</v>
+        <v>0.9066</v>
       </c>
       <c r="F168" t="n">
-        <v>0.9256</v>
+        <v>0.912</v>
       </c>
       <c r="G168" t="n">
-        <v>0.9193</v>
+        <v>0.9377</v>
       </c>
       <c r="H168" t="n">
-        <v>0.9522</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="I168" t="n">
-        <v>0.8942</v>
+        <v>0.9462</v>
       </c>
       <c r="J168" t="n">
-        <v>0.946</v>
+        <v>0.9039</v>
       </c>
       <c r="K168" t="n">
-        <v>0.9581</v>
+        <v>0.9205</v>
       </c>
       <c r="L168" t="n">
-        <v>0.9258</v>
+        <v>0.9224</v>
       </c>
       <c r="M168" t="n">
-        <v>0.023</v>
+        <v>0.0155</v>
       </c>
     </row>
     <row r="169">
@@ -7805,40 +8230,40 @@
         </is>
       </c>
       <c r="B169" t="n">
-        <v>0.6854</v>
+        <v>0.7159</v>
       </c>
       <c r="C169" t="n">
-        <v>0.714</v>
+        <v>0.7603</v>
       </c>
       <c r="D169" t="n">
-        <v>0.6994</v>
+        <v>0.7554</v>
       </c>
       <c r="E169" t="n">
-        <v>0.8559</v>
+        <v>0.6883</v>
       </c>
       <c r="F169" t="n">
-        <v>0.7482</v>
+        <v>0.6777</v>
       </c>
       <c r="G169" t="n">
-        <v>0.6866</v>
+        <v>0.7197</v>
       </c>
       <c r="H169" t="n">
-        <v>0.7471</v>
+        <v>0.8492</v>
       </c>
       <c r="I169" t="n">
-        <v>0.7689</v>
+        <v>0.7262</v>
       </c>
       <c r="J169" t="n">
-        <v>0.7544</v>
+        <v>0.6447000000000001</v>
       </c>
       <c r="K169" t="n">
-        <v>0.6895</v>
+        <v>0.768</v>
       </c>
       <c r="L169" t="n">
-        <v>0.7349</v>
+        <v>0.7305</v>
       </c>
       <c r="M169" t="n">
-        <v>0.0528</v>
+        <v>0.057</v>
       </c>
     </row>
     <row r="170">
@@ -7848,46 +8273,46 @@
         </is>
       </c>
       <c r="B170" t="n">
-        <v>0.9658</v>
+        <v>1.0779</v>
       </c>
       <c r="C170" t="n">
-        <v>1.0398</v>
+        <v>1.0263</v>
       </c>
       <c r="D170" t="n">
-        <v>0.9795</v>
+        <v>0.9781</v>
       </c>
       <c r="E170" t="n">
-        <v>1.008</v>
+        <v>1.0169</v>
       </c>
       <c r="F170" t="n">
-        <v>0.9663</v>
+        <v>0.9594</v>
       </c>
       <c r="G170" t="n">
-        <v>0.9921</v>
+        <v>1.0114</v>
       </c>
       <c r="H170" t="n">
-        <v>0.999</v>
+        <v>0.9898</v>
       </c>
       <c r="I170" t="n">
-        <v>1.0319</v>
+        <v>1.0194</v>
       </c>
       <c r="J170" t="n">
-        <v>1.0283</v>
+        <v>1.0757</v>
       </c>
       <c r="K170" t="n">
-        <v>0.9875</v>
+        <v>0.991</v>
       </c>
       <c r="L170" t="n">
-        <v>0.9998</v>
+        <v>1.0146</v>
       </c>
       <c r="M170" t="n">
-        <v>0.0267</v>
+        <v>0.0387</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="1" t="inlineStr">
         <is>
-          <t>augmented — RMSSE</t>
+          <t>SPCP — RMSSE</t>
         </is>
       </c>
     </row>
@@ -7965,40 +8390,40 @@
         </is>
       </c>
       <c r="B174" t="n">
-        <v>0.2995</v>
+        <v>0.2783</v>
       </c>
       <c r="C174" t="n">
-        <v>0.3292</v>
+        <v>0.2987</v>
       </c>
       <c r="D174" t="n">
-        <v>0.3187</v>
+        <v>0.2994</v>
       </c>
       <c r="E174" t="n">
-        <v>0.3122</v>
+        <v>0.3053</v>
       </c>
       <c r="F174" t="n">
-        <v>0.3025</v>
+        <v>0.2833</v>
       </c>
       <c r="G174" t="n">
-        <v>0.2992</v>
+        <v>0.2783</v>
       </c>
       <c r="H174" t="n">
-        <v>0.3015</v>
+        <v>0.3138</v>
       </c>
       <c r="I174" t="n">
-        <v>0.3074</v>
+        <v>0.2851</v>
       </c>
       <c r="J174" t="n">
-        <v>0.2975</v>
+        <v>0.2977</v>
       </c>
       <c r="K174" t="n">
-        <v>0.2977</v>
+        <v>0.2946</v>
       </c>
       <c r="L174" t="n">
-        <v>0.3065</v>
+        <v>0.2935</v>
       </c>
       <c r="M174" t="n">
-        <v>0.0105</v>
+        <v>0.0119</v>
       </c>
     </row>
     <row r="175">
@@ -8008,40 +8433,40 @@
         </is>
       </c>
       <c r="B175" t="n">
-        <v>1.0747</v>
+        <v>1.111</v>
       </c>
       <c r="C175" t="n">
-        <v>1.0659</v>
+        <v>1.0914</v>
       </c>
       <c r="D175" t="n">
-        <v>1.0762</v>
+        <v>1.0592</v>
       </c>
       <c r="E175" t="n">
-        <v>1.0468</v>
+        <v>1.0658</v>
       </c>
       <c r="F175" t="n">
-        <v>1.0475</v>
+        <v>1.0773</v>
       </c>
       <c r="G175" t="n">
-        <v>1.0784</v>
+        <v>1.0816</v>
       </c>
       <c r="H175" t="n">
-        <v>1.0456</v>
+        <v>1.091</v>
       </c>
       <c r="I175" t="n">
-        <v>1.0454</v>
+        <v>1.0815</v>
       </c>
       <c r="J175" t="n">
-        <v>1.0911</v>
+        <v>1.0844</v>
       </c>
       <c r="K175" t="n">
-        <v>1.0953</v>
+        <v>1.0719</v>
       </c>
       <c r="L175" t="n">
-        <v>1.0667</v>
+        <v>1.0815</v>
       </c>
       <c r="M175" t="n">
-        <v>0.0193</v>
+        <v>0.0146</v>
       </c>
     </row>
     <row r="176">
@@ -8051,40 +8476,40 @@
         </is>
       </c>
       <c r="B176" t="n">
-        <v>0.5599</v>
+        <v>0.5813</v>
       </c>
       <c r="C176" t="n">
-        <v>0.5471</v>
+        <v>0.5435</v>
       </c>
       <c r="D176" t="n">
-        <v>0.5293</v>
+        <v>0.5505</v>
       </c>
       <c r="E176" t="n">
-        <v>0.5644</v>
+        <v>0.5435</v>
       </c>
       <c r="F176" t="n">
-        <v>0.5427999999999999</v>
+        <v>0.5741000000000001</v>
       </c>
       <c r="G176" t="n">
-        <v>0.5306999999999999</v>
+        <v>0.5965</v>
       </c>
       <c r="H176" t="n">
-        <v>0.5611</v>
+        <v>0.5667</v>
       </c>
       <c r="I176" t="n">
-        <v>0.5379</v>
+        <v>0.5444</v>
       </c>
       <c r="J176" t="n">
-        <v>0.5605</v>
+        <v>0.5325</v>
       </c>
       <c r="K176" t="n">
-        <v>0.5256999999999999</v>
+        <v>0.5685</v>
       </c>
       <c r="L176" t="n">
-        <v>0.5459000000000001</v>
+        <v>0.5602</v>
       </c>
       <c r="M176" t="n">
-        <v>0.0148</v>
+        <v>0.0204</v>
       </c>
     </row>
     <row r="177">
@@ -8094,40 +8519,40 @@
         </is>
       </c>
       <c r="B177" t="n">
-        <v>0.951</v>
+        <v>0.9592000000000001</v>
       </c>
       <c r="C177" t="n">
-        <v>0.9731</v>
+        <v>0.9741</v>
       </c>
       <c r="D177" t="n">
-        <v>0.9686</v>
+        <v>0.9826</v>
       </c>
       <c r="E177" t="n">
-        <v>0.9436</v>
+        <v>0.9673</v>
       </c>
       <c r="F177" t="n">
-        <v>0.9744</v>
+        <v>0.9918</v>
       </c>
       <c r="G177" t="n">
-        <v>0.9293</v>
+        <v>0.9624</v>
       </c>
       <c r="H177" t="n">
-        <v>0.9508</v>
+        <v>0.958</v>
       </c>
       <c r="I177" t="n">
-        <v>0.9216</v>
+        <v>0.9776</v>
       </c>
       <c r="J177" t="n">
-        <v>0.9408</v>
+        <v>0.9747</v>
       </c>
       <c r="K177" t="n">
-        <v>0.9728</v>
+        <v>0.9555</v>
       </c>
       <c r="L177" t="n">
-        <v>0.9526</v>
+        <v>0.9703000000000001</v>
       </c>
       <c r="M177" t="n">
-        <v>0.0191</v>
+        <v>0.0119</v>
       </c>
     </row>
     <row r="178">
@@ -8137,40 +8562,40 @@
         </is>
       </c>
       <c r="B178" t="n">
-        <v>1.0733</v>
+        <v>1.0439</v>
       </c>
       <c r="C178" t="n">
-        <v>1.0832</v>
+        <v>1.0947</v>
       </c>
       <c r="D178" t="n">
-        <v>1.0892</v>
+        <v>1.1089</v>
       </c>
       <c r="E178" t="n">
-        <v>1.0874</v>
+        <v>1.1294</v>
       </c>
       <c r="F178" t="n">
-        <v>1.0481</v>
+        <v>1.0935</v>
       </c>
       <c r="G178" t="n">
-        <v>1.0777</v>
+        <v>1.0503</v>
       </c>
       <c r="H178" t="n">
-        <v>1.0953</v>
+        <v>1.1034</v>
       </c>
       <c r="I178" t="n">
-        <v>1.0762</v>
+        <v>1.0508</v>
       </c>
       <c r="J178" t="n">
-        <v>1.0588</v>
+        <v>1.0901</v>
       </c>
       <c r="K178" t="n">
-        <v>1.048</v>
+        <v>1.0961</v>
       </c>
       <c r="L178" t="n">
-        <v>1.0737</v>
+        <v>1.0861</v>
       </c>
       <c r="M178" t="n">
-        <v>0.0168</v>
+        <v>0.0284</v>
       </c>
     </row>
     <row r="179">
@@ -8180,40 +8605,40 @@
         </is>
       </c>
       <c r="B179" t="n">
-        <v>0.4851</v>
+        <v>0.4739</v>
       </c>
       <c r="C179" t="n">
-        <v>0.4879</v>
+        <v>0.4897</v>
       </c>
       <c r="D179" t="n">
-        <v>0.4852</v>
+        <v>0.4955</v>
       </c>
       <c r="E179" t="n">
-        <v>0.4766</v>
+        <v>0.4947</v>
       </c>
       <c r="F179" t="n">
-        <v>0.4868</v>
+        <v>0.488</v>
       </c>
       <c r="G179" t="n">
-        <v>0.4921</v>
+        <v>0.4777</v>
       </c>
       <c r="H179" t="n">
-        <v>0.4904</v>
+        <v>0.4819</v>
       </c>
       <c r="I179" t="n">
-        <v>0.4893</v>
+        <v>0.4764</v>
       </c>
       <c r="J179" t="n">
-        <v>0.4894</v>
+        <v>0.4994</v>
       </c>
       <c r="K179" t="n">
-        <v>0.4855</v>
+        <v>0.487</v>
       </c>
       <c r="L179" t="n">
-        <v>0.4868</v>
+        <v>0.4864</v>
       </c>
       <c r="M179" t="n">
-        <v>0.0043</v>
+        <v>0.008699999999999999</v>
       </c>
     </row>
     <row r="180">
@@ -8223,40 +8648,40 @@
         </is>
       </c>
       <c r="B180" t="n">
-        <v>1.1028</v>
+        <v>0.9931</v>
       </c>
       <c r="C180" t="n">
-        <v>1.1578</v>
+        <v>1.0879</v>
       </c>
       <c r="D180" t="n">
-        <v>1.115</v>
+        <v>1.0576</v>
       </c>
       <c r="E180" t="n">
-        <v>1.1271</v>
+        <v>1.0961</v>
       </c>
       <c r="F180" t="n">
-        <v>1.0898</v>
+        <v>1.0323</v>
       </c>
       <c r="G180" t="n">
-        <v>1.0712</v>
+        <v>1.029</v>
       </c>
       <c r="H180" t="n">
-        <v>1.1209</v>
+        <v>1.0445</v>
       </c>
       <c r="I180" t="n">
-        <v>1.1356</v>
+        <v>1.0756</v>
       </c>
       <c r="J180" t="n">
-        <v>1.1511</v>
+        <v>1.0762</v>
       </c>
       <c r="K180" t="n">
-        <v>1.1058</v>
+        <v>1.0678</v>
       </c>
       <c r="L180" t="n">
-        <v>1.1177</v>
+        <v>1.056</v>
       </c>
       <c r="M180" t="n">
-        <v>0.0268</v>
+        <v>0.0315</v>
       </c>
     </row>
     <row r="181">
@@ -8266,40 +8691,40 @@
         </is>
       </c>
       <c r="B181" t="n">
-        <v>0.9635</v>
+        <v>0.9722</v>
       </c>
       <c r="C181" t="n">
-        <v>0.974</v>
+        <v>0.9595</v>
       </c>
       <c r="D181" t="n">
-        <v>0.9635</v>
+        <v>0.9614</v>
       </c>
       <c r="E181" t="n">
-        <v>0.9335</v>
+        <v>0.9609</v>
       </c>
       <c r="F181" t="n">
-        <v>0.9545</v>
+        <v>0.9565</v>
       </c>
       <c r="G181" t="n">
-        <v>0.9744</v>
+        <v>0.9781</v>
       </c>
       <c r="H181" t="n">
-        <v>0.9743000000000001</v>
+        <v>0.9298999999999999</v>
       </c>
       <c r="I181" t="n">
-        <v>0.967</v>
+        <v>0.9797</v>
       </c>
       <c r="J181" t="n">
-        <v>0.9795</v>
+        <v>0.9628</v>
       </c>
       <c r="K181" t="n">
-        <v>0.9811</v>
+        <v>0.9553</v>
       </c>
       <c r="L181" t="n">
-        <v>0.9665</v>
+        <v>0.9616</v>
       </c>
       <c r="M181" t="n">
-        <v>0.0142</v>
+        <v>0.0141</v>
       </c>
     </row>
     <row r="182">
@@ -8309,40 +8734,40 @@
         </is>
       </c>
       <c r="B182" t="n">
-        <v>0.5555</v>
+        <v>0.5944</v>
       </c>
       <c r="C182" t="n">
-        <v>0.5528999999999999</v>
+        <v>0.6017</v>
       </c>
       <c r="D182" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.5969</v>
       </c>
       <c r="E182" t="n">
-        <v>0.6482</v>
+        <v>0.5596</v>
       </c>
       <c r="F182" t="n">
-        <v>0.5891999999999999</v>
+        <v>0.5445</v>
       </c>
       <c r="G182" t="n">
-        <v>0.5426</v>
+        <v>0.57</v>
       </c>
       <c r="H182" t="n">
-        <v>0.5853</v>
+        <v>0.618</v>
       </c>
       <c r="I182" t="n">
-        <v>0.5848</v>
+        <v>0.5644</v>
       </c>
       <c r="J182" t="n">
-        <v>0.5921999999999999</v>
+        <v>0.539</v>
       </c>
       <c r="K182" t="n">
-        <v>0.5508999999999999</v>
+        <v>0.5857</v>
       </c>
       <c r="L182" t="n">
-        <v>0.5766</v>
+        <v>0.5774</v>
       </c>
       <c r="M182" t="n">
-        <v>0.031</v>
+        <v>0.026</v>
       </c>
     </row>
     <row r="183">
@@ -8352,46 +8777,46 @@
         </is>
       </c>
       <c r="B183" t="n">
-        <v>0.9</v>
+        <v>0.9263</v>
       </c>
       <c r="C183" t="n">
-        <v>0.9256</v>
+        <v>0.9127</v>
       </c>
       <c r="D183" t="n">
-        <v>0.9015</v>
+        <v>0.884</v>
       </c>
       <c r="E183" t="n">
-        <v>0.9123</v>
+        <v>0.8877</v>
       </c>
       <c r="F183" t="n">
-        <v>0.8769</v>
+        <v>0.8842</v>
       </c>
       <c r="G183" t="n">
-        <v>0.9222</v>
+        <v>0.9171</v>
       </c>
       <c r="H183" t="n">
-        <v>0.9111</v>
+        <v>0.8903</v>
       </c>
       <c r="I183" t="n">
-        <v>0.9014</v>
+        <v>0.906</v>
       </c>
       <c r="J183" t="n">
-        <v>0.9204</v>
+        <v>0.9332</v>
       </c>
       <c r="K183" t="n">
-        <v>0.9113</v>
+        <v>0.8973</v>
       </c>
       <c r="L183" t="n">
-        <v>0.9083</v>
+        <v>0.9039</v>
       </c>
       <c r="M183" t="n">
-        <v>0.0142</v>
+        <v>0.0179</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="1" t="inlineStr">
         <is>
-          <t>r+r — MASE</t>
+          <t>augmented — MASE</t>
         </is>
       </c>
     </row>
@@ -8469,40 +8894,40 @@
         </is>
       </c>
       <c r="B187" t="n">
-        <v>0.4072</v>
+        <v>0.4083</v>
       </c>
       <c r="C187" t="n">
-        <v>0.4387</v>
+        <v>0.4471</v>
       </c>
       <c r="D187" t="n">
-        <v>0.451</v>
+        <v>0.4636</v>
       </c>
       <c r="E187" t="n">
-        <v>0.437</v>
+        <v>0.4436</v>
       </c>
       <c r="F187" t="n">
-        <v>0.399</v>
+        <v>0.3956</v>
       </c>
       <c r="G187" t="n">
-        <v>0.417</v>
+        <v>0.424</v>
       </c>
       <c r="H187" t="n">
-        <v>0.4332</v>
+        <v>0.4357</v>
       </c>
       <c r="I187" t="n">
-        <v>0.4293</v>
+        <v>0.4333</v>
       </c>
       <c r="J187" t="n">
-        <v>0.3948</v>
+        <v>0.4111</v>
       </c>
       <c r="K187" t="n">
-        <v>0.3904</v>
+        <v>0.4166</v>
       </c>
       <c r="L187" t="n">
-        <v>0.4197</v>
+        <v>0.4279</v>
       </c>
       <c r="M187" t="n">
-        <v>0.021</v>
+        <v>0.0206</v>
       </c>
     </row>
     <row r="188">
@@ -8512,40 +8937,40 @@
         </is>
       </c>
       <c r="B188" t="n">
-        <v>1.051</v>
+        <v>1.0278</v>
       </c>
       <c r="C188" t="n">
-        <v>1.0976</v>
+        <v>1.0577</v>
       </c>
       <c r="D188" t="n">
-        <v>1.1188</v>
+        <v>1.0985</v>
       </c>
       <c r="E188" t="n">
-        <v>1.098</v>
+        <v>1.0722</v>
       </c>
       <c r="F188" t="n">
-        <v>1.0547</v>
+        <v>1.0301</v>
       </c>
       <c r="G188" t="n">
-        <v>1.0862</v>
+        <v>1.0613</v>
       </c>
       <c r="H188" t="n">
-        <v>1.091</v>
+        <v>1.0474</v>
       </c>
       <c r="I188" t="n">
-        <v>1.0705</v>
+        <v>1.0602</v>
       </c>
       <c r="J188" t="n">
-        <v>1.123</v>
+        <v>1.1184</v>
       </c>
       <c r="K188" t="n">
-        <v>1.0833</v>
+        <v>1.073</v>
       </c>
       <c r="L188" t="n">
-        <v>1.0874</v>
+        <v>1.0647</v>
       </c>
       <c r="M188" t="n">
-        <v>0.024</v>
+        <v>0.0281</v>
       </c>
     </row>
     <row r="189">
@@ -8555,40 +8980,40 @@
         </is>
       </c>
       <c r="B189" t="n">
-        <v>0.9282</v>
+        <v>0.9396</v>
       </c>
       <c r="C189" t="n">
-        <v>0.9963</v>
+        <v>0.9609</v>
       </c>
       <c r="D189" t="n">
-        <v>0.9671</v>
+        <v>0.9239000000000001</v>
       </c>
       <c r="E189" t="n">
-        <v>0.9854000000000001</v>
+        <v>0.9234</v>
       </c>
       <c r="F189" t="n">
-        <v>0.9139</v>
+        <v>0.8829</v>
       </c>
       <c r="G189" t="n">
-        <v>0.8588</v>
+        <v>0.8377</v>
       </c>
       <c r="H189" t="n">
-        <v>1.0027</v>
+        <v>0.9336</v>
       </c>
       <c r="I189" t="n">
-        <v>0.8787</v>
+        <v>0.8428</v>
       </c>
       <c r="J189" t="n">
-        <v>0.9413</v>
+        <v>0.9125</v>
       </c>
       <c r="K189" t="n">
-        <v>0.9538</v>
+        <v>0.9462</v>
       </c>
       <c r="L189" t="n">
-        <v>0.9426</v>
+        <v>0.9104</v>
       </c>
       <c r="M189" t="n">
-        <v>0.0485</v>
+        <v>0.0424</v>
       </c>
     </row>
     <row r="190">
@@ -8598,40 +9023,40 @@
         </is>
       </c>
       <c r="B190" t="n">
-        <v>0.976</v>
+        <v>0.9794</v>
       </c>
       <c r="C190" t="n">
-        <v>1.0255</v>
+        <v>0.9993</v>
       </c>
       <c r="D190" t="n">
-        <v>1.0404</v>
+        <v>1.0145</v>
       </c>
       <c r="E190" t="n">
-        <v>0.989</v>
+        <v>0.986</v>
       </c>
       <c r="F190" t="n">
-        <v>1.0424</v>
+        <v>1.0237</v>
       </c>
       <c r="G190" t="n">
-        <v>0.9992</v>
+        <v>0.9893999999999999</v>
       </c>
       <c r="H190" t="n">
-        <v>0.9708</v>
+        <v>0.9525</v>
       </c>
       <c r="I190" t="n">
-        <v>1.0096</v>
+        <v>0.991</v>
       </c>
       <c r="J190" t="n">
-        <v>0.9888</v>
+        <v>1.0154</v>
       </c>
       <c r="K190" t="n">
-        <v>1.0682</v>
+        <v>1.0602</v>
       </c>
       <c r="L190" t="n">
-        <v>1.011</v>
+        <v>1.0011</v>
       </c>
       <c r="M190" t="n">
-        <v>0.0321</v>
+        <v>0.0293</v>
       </c>
     </row>
     <row r="191">
@@ -8641,40 +9066,40 @@
         </is>
       </c>
       <c r="B191" t="n">
-        <v>1.2345</v>
+        <v>1.2246</v>
       </c>
       <c r="C191" t="n">
-        <v>1.2863</v>
+        <v>1.2725</v>
       </c>
       <c r="D191" t="n">
-        <v>1.2148</v>
+        <v>1.232</v>
       </c>
       <c r="E191" t="n">
-        <v>1.2912</v>
+        <v>1.2818</v>
       </c>
       <c r="F191" t="n">
-        <v>1.2077</v>
+        <v>1.1939</v>
       </c>
       <c r="G191" t="n">
-        <v>1.2843</v>
+        <v>1.2961</v>
       </c>
       <c r="H191" t="n">
-        <v>1.2478</v>
+        <v>1.2475</v>
       </c>
       <c r="I191" t="n">
-        <v>1.2548</v>
+        <v>1.2533</v>
       </c>
       <c r="J191" t="n">
-        <v>1.2118</v>
+        <v>1.2217</v>
       </c>
       <c r="K191" t="n">
-        <v>1.1722</v>
+        <v>1.2083</v>
       </c>
       <c r="L191" t="n">
-        <v>1.2405</v>
+        <v>1.2432</v>
       </c>
       <c r="M191" t="n">
-        <v>0.0396</v>
+        <v>0.0331</v>
       </c>
     </row>
     <row r="192">
@@ -8684,40 +9109,40 @@
         </is>
       </c>
       <c r="B192" t="n">
-        <v>0.4488</v>
+        <v>0.4558</v>
       </c>
       <c r="C192" t="n">
-        <v>0.4532</v>
+        <v>0.4688</v>
       </c>
       <c r="D192" t="n">
-        <v>0.433</v>
+        <v>0.4371</v>
       </c>
       <c r="E192" t="n">
-        <v>0.4522</v>
+        <v>0.4387</v>
       </c>
       <c r="F192" t="n">
-        <v>0.4324</v>
+        <v>0.4288</v>
       </c>
       <c r="G192" t="n">
-        <v>0.4627</v>
+        <v>0.472</v>
       </c>
       <c r="H192" t="n">
-        <v>0.4359</v>
+        <v>0.4472</v>
       </c>
       <c r="I192" t="n">
-        <v>0.4583</v>
+        <v>0.4652</v>
       </c>
       <c r="J192" t="n">
-        <v>0.4682</v>
+        <v>0.4604</v>
       </c>
       <c r="K192" t="n">
-        <v>0.4259</v>
+        <v>0.4412</v>
       </c>
       <c r="L192" t="n">
-        <v>0.4471</v>
+        <v>0.4515</v>
       </c>
       <c r="M192" t="n">
-        <v>0.0144</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="193">
@@ -8727,40 +9152,40 @@
         </is>
       </c>
       <c r="B193" t="n">
-        <v>1.5408</v>
+        <v>1.4963</v>
       </c>
       <c r="C193" t="n">
-        <v>1.6259</v>
+        <v>1.5907</v>
       </c>
       <c r="D193" t="n">
-        <v>1.5971</v>
+        <v>1.5302</v>
       </c>
       <c r="E193" t="n">
-        <v>1.5316</v>
+        <v>1.5106</v>
       </c>
       <c r="F193" t="n">
-        <v>1.5193</v>
+        <v>1.4677</v>
       </c>
       <c r="G193" t="n">
-        <v>1.6286</v>
+        <v>1.5399</v>
       </c>
       <c r="H193" t="n">
-        <v>1.5106</v>
+        <v>1.4491</v>
       </c>
       <c r="I193" t="n">
-        <v>1.5723</v>
+        <v>1.5173</v>
       </c>
       <c r="J193" t="n">
-        <v>1.6475</v>
+        <v>1.6226</v>
       </c>
       <c r="K193" t="n">
-        <v>1.4921</v>
+        <v>1.5065</v>
       </c>
       <c r="L193" t="n">
-        <v>1.5666</v>
+        <v>1.5231</v>
       </c>
       <c r="M193" t="n">
-        <v>0.0555</v>
+        <v>0.0522</v>
       </c>
     </row>
     <row r="194">
@@ -8770,40 +9195,40 @@
         </is>
       </c>
       <c r="B194" t="n">
-        <v>0.9073</v>
+        <v>0.9107</v>
       </c>
       <c r="C194" t="n">
-        <v>0.907</v>
+        <v>0.9063</v>
       </c>
       <c r="D194" t="n">
-        <v>0.9067</v>
+        <v>0.9003</v>
       </c>
       <c r="E194" t="n">
-        <v>0.8696</v>
+        <v>0.8879</v>
       </c>
       <c r="F194" t="n">
-        <v>0.9298</v>
+        <v>0.9236</v>
       </c>
       <c r="G194" t="n">
-        <v>0.9029</v>
+        <v>0.9123</v>
       </c>
       <c r="H194" t="n">
-        <v>0.9169</v>
+        <v>0.9094</v>
       </c>
       <c r="I194" t="n">
-        <v>0.8535</v>
+        <v>0.8572</v>
       </c>
       <c r="J194" t="n">
-        <v>0.9545</v>
+        <v>0.9419</v>
       </c>
       <c r="K194" t="n">
-        <v>0.9655</v>
+        <v>0.9657</v>
       </c>
       <c r="L194" t="n">
-        <v>0.9114</v>
+        <v>0.9115</v>
       </c>
       <c r="M194" t="n">
-        <v>0.034</v>
+        <v>0.0292</v>
       </c>
     </row>
     <row r="195">
@@ -8813,40 +9238,40 @@
         </is>
       </c>
       <c r="B195" t="n">
-        <v>0.7266</v>
+        <v>0.7261</v>
       </c>
       <c r="C195" t="n">
-        <v>0.7905</v>
+        <v>0.7574</v>
       </c>
       <c r="D195" t="n">
-        <v>0.7611</v>
+        <v>0.7466</v>
       </c>
       <c r="E195" t="n">
-        <v>0.7818000000000001</v>
+        <v>0.7472</v>
       </c>
       <c r="F195" t="n">
-        <v>0.7352</v>
+        <v>0.7174</v>
       </c>
       <c r="G195" t="n">
-        <v>0.7284</v>
+        <v>0.7007</v>
       </c>
       <c r="H195" t="n">
-        <v>0.7625</v>
+        <v>0.731</v>
       </c>
       <c r="I195" t="n">
-        <v>0.7903</v>
+        <v>0.7804</v>
       </c>
       <c r="J195" t="n">
-        <v>0.7694</v>
+        <v>0.7629</v>
       </c>
       <c r="K195" t="n">
-        <v>0.7458</v>
+        <v>0.7532</v>
       </c>
       <c r="L195" t="n">
-        <v>0.7592</v>
+        <v>0.7423</v>
       </c>
       <c r="M195" t="n">
-        <v>0.0244</v>
+        <v>0.0236</v>
       </c>
     </row>
     <row r="196">
@@ -8856,46 +9281,46 @@
         </is>
       </c>
       <c r="B196" t="n">
-        <v>0.9913999999999999</v>
+        <v>1.0002</v>
       </c>
       <c r="C196" t="n">
-        <v>0.9851</v>
+        <v>0.9839</v>
       </c>
       <c r="D196" t="n">
-        <v>0.9962</v>
+        <v>1.0132</v>
       </c>
       <c r="E196" t="n">
-        <v>1.0136</v>
+        <v>1.0459</v>
       </c>
       <c r="F196" t="n">
-        <v>1.0235</v>
+        <v>1.0315</v>
       </c>
       <c r="G196" t="n">
-        <v>0.9754</v>
+        <v>0.984</v>
       </c>
       <c r="H196" t="n">
-        <v>0.9916</v>
+        <v>1.0126</v>
       </c>
       <c r="I196" t="n">
-        <v>0.9918</v>
+        <v>1.0093</v>
       </c>
       <c r="J196" t="n">
-        <v>1.0148</v>
+        <v>1.0365</v>
       </c>
       <c r="K196" t="n">
-        <v>1.0378</v>
+        <v>1.0252</v>
       </c>
       <c r="L196" t="n">
-        <v>1.0021</v>
+        <v>1.0142</v>
       </c>
       <c r="M196" t="n">
-        <v>0.0194</v>
+        <v>0.021</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="1" t="inlineStr">
         <is>
-          <t>r+r — RMSSE</t>
+          <t>augmented — RMSSE</t>
         </is>
       </c>
     </row>
@@ -8973,40 +9398,40 @@
         </is>
       </c>
       <c r="B200" t="n">
-        <v>0.2945</v>
+        <v>0.2922</v>
       </c>
       <c r="C200" t="n">
-        <v>0.2994</v>
+        <v>0.3005</v>
       </c>
       <c r="D200" t="n">
-        <v>0.3014</v>
+        <v>0.3002</v>
       </c>
       <c r="E200" t="n">
-        <v>0.2949</v>
+        <v>0.2959</v>
       </c>
       <c r="F200" t="n">
-        <v>0.2877</v>
+        <v>0.2851</v>
       </c>
       <c r="G200" t="n">
-        <v>0.2833</v>
+        <v>0.2868</v>
       </c>
       <c r="H200" t="n">
-        <v>0.2899</v>
+        <v>0.2911</v>
       </c>
       <c r="I200" t="n">
-        <v>0.2915</v>
+        <v>0.288</v>
       </c>
       <c r="J200" t="n">
-        <v>0.2718</v>
+        <v>0.2736</v>
       </c>
       <c r="K200" t="n">
-        <v>0.2771</v>
+        <v>0.2847</v>
       </c>
       <c r="L200" t="n">
-        <v>0.2891</v>
+        <v>0.2898</v>
       </c>
       <c r="M200" t="n">
-        <v>0.0095</v>
+        <v>0.0081</v>
       </c>
     </row>
     <row r="201">
@@ -9016,40 +9441,40 @@
         </is>
       </c>
       <c r="B201" t="n">
-        <v>1.0717</v>
+        <v>1.0741</v>
       </c>
       <c r="C201" t="n">
-        <v>1.0517</v>
+        <v>1.0479</v>
       </c>
       <c r="D201" t="n">
-        <v>1.0873</v>
+        <v>1.0904</v>
       </c>
       <c r="E201" t="n">
-        <v>1.0613</v>
+        <v>1.0596</v>
       </c>
       <c r="F201" t="n">
-        <v>1.0579</v>
+        <v>1.0547</v>
       </c>
       <c r="G201" t="n">
-        <v>1.0707</v>
+        <v>1.0667</v>
       </c>
       <c r="H201" t="n">
-        <v>1.0614</v>
+        <v>1.0521</v>
       </c>
       <c r="I201" t="n">
-        <v>1.0489</v>
+        <v>1.0513</v>
       </c>
       <c r="J201" t="n">
-        <v>1.0913</v>
+        <v>1.0966</v>
       </c>
       <c r="K201" t="n">
-        <v>1.084</v>
+        <v>1.0821</v>
       </c>
       <c r="L201" t="n">
-        <v>1.0686</v>
+        <v>1.0675</v>
       </c>
       <c r="M201" t="n">
-        <v>0.015</v>
+        <v>0.0174</v>
       </c>
     </row>
     <row r="202">
@@ -9059,40 +9484,40 @@
         </is>
       </c>
       <c r="B202" t="n">
-        <v>0.5623</v>
+        <v>0.5699</v>
       </c>
       <c r="C202" t="n">
-        <v>0.5897</v>
+        <v>0.5762</v>
       </c>
       <c r="D202" t="n">
-        <v>0.5803</v>
+        <v>0.5674</v>
       </c>
       <c r="E202" t="n">
-        <v>0.5878</v>
+        <v>0.569</v>
       </c>
       <c r="F202" t="n">
-        <v>0.5566</v>
+        <v>0.5501</v>
       </c>
       <c r="G202" t="n">
-        <v>0.5236</v>
+        <v>0.5192</v>
       </c>
       <c r="H202" t="n">
-        <v>0.595</v>
+        <v>0.577</v>
       </c>
       <c r="I202" t="n">
-        <v>0.5359</v>
+        <v>0.5266999999999999</v>
       </c>
       <c r="J202" t="n">
-        <v>0.5986</v>
+        <v>0.5869</v>
       </c>
       <c r="K202" t="n">
-        <v>0.5856</v>
+        <v>0.5949</v>
       </c>
       <c r="L202" t="n">
-        <v>0.5715</v>
+        <v>0.5637</v>
       </c>
       <c r="M202" t="n">
-        <v>0.0259</v>
+        <v>0.0246</v>
       </c>
     </row>
     <row r="203">
@@ -9102,40 +9527,40 @@
         </is>
       </c>
       <c r="B203" t="n">
-        <v>0.9529</v>
+        <v>0.9508</v>
       </c>
       <c r="C203" t="n">
-        <v>0.9641999999999999</v>
+        <v>0.9526</v>
       </c>
       <c r="D203" t="n">
-        <v>0.974</v>
+        <v>0.9671999999999999</v>
       </c>
       <c r="E203" t="n">
-        <v>0.9282</v>
+        <v>0.9443</v>
       </c>
       <c r="F203" t="n">
-        <v>0.9874000000000001</v>
+        <v>0.9929</v>
       </c>
       <c r="G203" t="n">
-        <v>0.9505</v>
+        <v>0.9448</v>
       </c>
       <c r="H203" t="n">
-        <v>0.9493</v>
+        <v>0.9532</v>
       </c>
       <c r="I203" t="n">
-        <v>0.9262</v>
+        <v>0.9232</v>
       </c>
       <c r="J203" t="n">
-        <v>0.9321</v>
+        <v>0.9513</v>
       </c>
       <c r="K203" t="n">
-        <v>0.9869</v>
+        <v>0.9796</v>
       </c>
       <c r="L203" t="n">
-        <v>0.9552</v>
+        <v>0.956</v>
       </c>
       <c r="M203" t="n">
-        <v>0.0227</v>
+        <v>0.0196</v>
       </c>
     </row>
     <row r="204">
@@ -9145,40 +9570,40 @@
         </is>
       </c>
       <c r="B204" t="n">
-        <v>1.061</v>
+        <v>1.064</v>
       </c>
       <c r="C204" t="n">
-        <v>1.0556</v>
+        <v>1.0736</v>
       </c>
       <c r="D204" t="n">
-        <v>1.0495</v>
+        <v>1.0568</v>
       </c>
       <c r="E204" t="n">
-        <v>1.0584</v>
+        <v>1.0675</v>
       </c>
       <c r="F204" t="n">
-        <v>1.0519</v>
+        <v>1.0517</v>
       </c>
       <c r="G204" t="n">
-        <v>1.0799</v>
+        <v>1.0983</v>
       </c>
       <c r="H204" t="n">
-        <v>1.0697</v>
+        <v>1.0863</v>
       </c>
       <c r="I204" t="n">
-        <v>1.0533</v>
+        <v>1.0554</v>
       </c>
       <c r="J204" t="n">
-        <v>1.0171</v>
+        <v>1.0368</v>
       </c>
       <c r="K204" t="n">
-        <v>1.0243</v>
+        <v>1.0428</v>
       </c>
       <c r="L204" t="n">
-        <v>1.0521</v>
+        <v>1.0633</v>
       </c>
       <c r="M204" t="n">
-        <v>0.0189</v>
+        <v>0.019</v>
       </c>
     </row>
     <row r="205">
@@ -9188,40 +9613,40 @@
         </is>
       </c>
       <c r="B205" t="n">
-        <v>0.4826</v>
+        <v>0.4813</v>
       </c>
       <c r="C205" t="n">
-        <v>0.4868</v>
+        <v>0.4931</v>
       </c>
       <c r="D205" t="n">
-        <v>0.4831</v>
+        <v>0.4845</v>
       </c>
       <c r="E205" t="n">
-        <v>0.4795</v>
+        <v>0.4778</v>
       </c>
       <c r="F205" t="n">
-        <v>0.4838</v>
+        <v>0.4812</v>
       </c>
       <c r="G205" t="n">
-        <v>0.4936</v>
+        <v>0.4977</v>
       </c>
       <c r="H205" t="n">
-        <v>0.4879</v>
+        <v>0.4921</v>
       </c>
       <c r="I205" t="n">
-        <v>0.4827</v>
+        <v>0.4822</v>
       </c>
       <c r="J205" t="n">
-        <v>0.4885</v>
+        <v>0.4859</v>
       </c>
       <c r="K205" t="n">
-        <v>0.4784</v>
+        <v>0.4785</v>
       </c>
       <c r="L205" t="n">
-        <v>0.4847</v>
+        <v>0.4854</v>
       </c>
       <c r="M205" t="n">
-        <v>0.0046</v>
+        <v>0.0067</v>
       </c>
     </row>
     <row r="206">
@@ -9231,40 +9656,40 @@
         </is>
       </c>
       <c r="B206" t="n">
-        <v>1.0997</v>
+        <v>1.0682</v>
       </c>
       <c r="C206" t="n">
-        <v>1.1226</v>
+        <v>1.0991</v>
       </c>
       <c r="D206" t="n">
-        <v>1.0819</v>
+        <v>1.0486</v>
       </c>
       <c r="E206" t="n">
-        <v>1.1017</v>
+        <v>1.0803</v>
       </c>
       <c r="F206" t="n">
-        <v>1.1052</v>
+        <v>1.0701</v>
       </c>
       <c r="G206" t="n">
-        <v>1.1079</v>
+        <v>1.0711</v>
       </c>
       <c r="H206" t="n">
-        <v>1.0807</v>
+        <v>1.0541</v>
       </c>
       <c r="I206" t="n">
-        <v>1.0959</v>
+        <v>1.0636</v>
       </c>
       <c r="J206" t="n">
-        <v>1.1433</v>
+        <v>1.1201</v>
       </c>
       <c r="K206" t="n">
-        <v>1.0773</v>
+        <v>1.0612</v>
       </c>
       <c r="L206" t="n">
-        <v>1.1016</v>
+        <v>1.0736</v>
       </c>
       <c r="M206" t="n">
-        <v>0.0202</v>
+        <v>0.0215</v>
       </c>
     </row>
     <row r="207">
@@ -9274,40 +9699,40 @@
         </is>
       </c>
       <c r="B207" t="n">
-        <v>0.9555</v>
+        <v>0.9641999999999999</v>
       </c>
       <c r="C207" t="n">
-        <v>0.9394</v>
+        <v>0.9492</v>
       </c>
       <c r="D207" t="n">
-        <v>0.9398</v>
+        <v>0.9475</v>
       </c>
       <c r="E207" t="n">
-        <v>0.926</v>
+        <v>0.9487</v>
       </c>
       <c r="F207" t="n">
-        <v>0.9459</v>
+        <v>0.9464</v>
       </c>
       <c r="G207" t="n">
-        <v>0.9547</v>
+        <v>0.963</v>
       </c>
       <c r="H207" t="n">
-        <v>0.9571</v>
+        <v>0.9687</v>
       </c>
       <c r="I207" t="n">
-        <v>0.9349</v>
+        <v>0.9468</v>
       </c>
       <c r="J207" t="n">
-        <v>0.9778</v>
+        <v>0.9743000000000001</v>
       </c>
       <c r="K207" t="n">
-        <v>0.9644</v>
+        <v>0.9604</v>
       </c>
       <c r="L207" t="n">
-        <v>0.9496</v>
+        <v>0.9569</v>
       </c>
       <c r="M207" t="n">
-        <v>0.0153</v>
+        <v>0.0104</v>
       </c>
     </row>
     <row r="208">
@@ -9317,40 +9742,40 @@
         </is>
       </c>
       <c r="B208" t="n">
-        <v>0.58</v>
+        <v>0.5795</v>
       </c>
       <c r="C208" t="n">
-        <v>0.5928</v>
+        <v>0.5784</v>
       </c>
       <c r="D208" t="n">
-        <v>0.5812</v>
+        <v>0.5694</v>
       </c>
       <c r="E208" t="n">
-        <v>0.6032</v>
+        <v>0.5807</v>
       </c>
       <c r="F208" t="n">
-        <v>0.5758</v>
+        <v>0.5813</v>
       </c>
       <c r="G208" t="n">
-        <v>0.5676</v>
+        <v>0.5492</v>
       </c>
       <c r="H208" t="n">
-        <v>0.5921999999999999</v>
+        <v>0.584</v>
       </c>
       <c r="I208" t="n">
-        <v>0.597</v>
+        <v>0.5844</v>
       </c>
       <c r="J208" t="n">
-        <v>0.5993000000000001</v>
+        <v>0.5926</v>
       </c>
       <c r="K208" t="n">
         <v>0.5648</v>
       </c>
       <c r="L208" t="n">
-        <v>0.5854</v>
+        <v>0.5764</v>
       </c>
       <c r="M208" t="n">
-        <v>0.0135</v>
+        <v>0.0123</v>
       </c>
     </row>
     <row r="209">
@@ -9360,39 +9785,1047 @@
         </is>
       </c>
       <c r="B209" t="n">
+        <v>0.9096</v>
+      </c>
+      <c r="C209" t="n">
+        <v>0.8984</v>
+      </c>
+      <c r="D209" t="n">
+        <v>0.9022</v>
+      </c>
+      <c r="E209" t="n">
+        <v>0.931</v>
+      </c>
+      <c r="F209" t="n">
+        <v>0.9113</v>
+      </c>
+      <c r="G209" t="n">
+        <v>0.894</v>
+      </c>
+      <c r="H209" t="n">
+        <v>0.9192</v>
+      </c>
+      <c r="I209" t="n">
+        <v>0.8927</v>
+      </c>
+      <c r="J209" t="n">
+        <v>0.9216</v>
+      </c>
+      <c r="K209" t="n">
+        <v>0.9056</v>
+      </c>
+      <c r="L209" t="n">
+        <v>0.9086</v>
+      </c>
+      <c r="M209" t="n">
+        <v>0.0125</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="1" t="inlineStr">
+        <is>
+          <t>r+r — MASE</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="1" t="inlineStr">
+        <is>
+          <t>household</t>
+        </is>
+      </c>
+      <c r="B212" s="1" t="inlineStr">
+        <is>
+          <t>seed0</t>
+        </is>
+      </c>
+      <c r="C212" s="1" t="inlineStr">
+        <is>
+          <t>seed1</t>
+        </is>
+      </c>
+      <c r="D212" s="1" t="inlineStr">
+        <is>
+          <t>seed2</t>
+        </is>
+      </c>
+      <c r="E212" s="1" t="inlineStr">
+        <is>
+          <t>seed3</t>
+        </is>
+      </c>
+      <c r="F212" s="1" t="inlineStr">
+        <is>
+          <t>seed4</t>
+        </is>
+      </c>
+      <c r="G212" s="1" t="inlineStr">
+        <is>
+          <t>seed5</t>
+        </is>
+      </c>
+      <c r="H212" s="1" t="inlineStr">
+        <is>
+          <t>seed6</t>
+        </is>
+      </c>
+      <c r="I212" s="1" t="inlineStr">
+        <is>
+          <t>seed7</t>
+        </is>
+      </c>
+      <c r="J212" s="1" t="inlineStr">
+        <is>
+          <t>seed8</t>
+        </is>
+      </c>
+      <c r="K212" s="1" t="inlineStr">
+        <is>
+          <t>seed9</t>
+        </is>
+      </c>
+      <c r="L212" s="1" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="M212" s="1" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>building11</t>
+        </is>
+      </c>
+      <c r="B213" t="n">
+        <v>0.4072</v>
+      </c>
+      <c r="C213" t="n">
+        <v>0.4387</v>
+      </c>
+      <c r="D213" t="n">
+        <v>0.451</v>
+      </c>
+      <c r="E213" t="n">
+        <v>0.437</v>
+      </c>
+      <c r="F213" t="n">
+        <v>0.399</v>
+      </c>
+      <c r="G213" t="n">
+        <v>0.417</v>
+      </c>
+      <c r="H213" t="n">
+        <v>0.4332</v>
+      </c>
+      <c r="I213" t="n">
+        <v>0.4293</v>
+      </c>
+      <c r="J213" t="n">
+        <v>0.3948</v>
+      </c>
+      <c r="K213" t="n">
+        <v>0.3904</v>
+      </c>
+      <c r="L213" t="n">
+        <v>0.4197</v>
+      </c>
+      <c r="M213" t="n">
+        <v>0.021</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>building13</t>
+        </is>
+      </c>
+      <c r="B214" t="n">
+        <v>1.051</v>
+      </c>
+      <c r="C214" t="n">
+        <v>1.0976</v>
+      </c>
+      <c r="D214" t="n">
+        <v>1.1188</v>
+      </c>
+      <c r="E214" t="n">
+        <v>1.098</v>
+      </c>
+      <c r="F214" t="n">
+        <v>1.0547</v>
+      </c>
+      <c r="G214" t="n">
+        <v>1.0862</v>
+      </c>
+      <c r="H214" t="n">
+        <v>1.091</v>
+      </c>
+      <c r="I214" t="n">
+        <v>1.0705</v>
+      </c>
+      <c r="J214" t="n">
+        <v>1.123</v>
+      </c>
+      <c r="K214" t="n">
+        <v>1.0833</v>
+      </c>
+      <c r="L214" t="n">
+        <v>1.0874</v>
+      </c>
+      <c r="M214" t="n">
+        <v>0.024</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>building17</t>
+        </is>
+      </c>
+      <c r="B215" t="n">
+        <v>0.9282</v>
+      </c>
+      <c r="C215" t="n">
+        <v>0.9963</v>
+      </c>
+      <c r="D215" t="n">
+        <v>0.9671</v>
+      </c>
+      <c r="E215" t="n">
+        <v>0.9854000000000001</v>
+      </c>
+      <c r="F215" t="n">
+        <v>0.9139</v>
+      </c>
+      <c r="G215" t="n">
+        <v>0.8588</v>
+      </c>
+      <c r="H215" t="n">
+        <v>1.0027</v>
+      </c>
+      <c r="I215" t="n">
+        <v>0.8787</v>
+      </c>
+      <c r="J215" t="n">
+        <v>0.9413</v>
+      </c>
+      <c r="K215" t="n">
+        <v>0.9538</v>
+      </c>
+      <c r="L215" t="n">
+        <v>0.9426</v>
+      </c>
+      <c r="M215" t="n">
+        <v>0.0485</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>building19</t>
+        </is>
+      </c>
+      <c r="B216" t="n">
+        <v>0.976</v>
+      </c>
+      <c r="C216" t="n">
+        <v>1.0255</v>
+      </c>
+      <c r="D216" t="n">
+        <v>1.0404</v>
+      </c>
+      <c r="E216" t="n">
+        <v>0.989</v>
+      </c>
+      <c r="F216" t="n">
+        <v>1.0424</v>
+      </c>
+      <c r="G216" t="n">
+        <v>0.9992</v>
+      </c>
+      <c r="H216" t="n">
+        <v>0.9708</v>
+      </c>
+      <c r="I216" t="n">
+        <v>1.0096</v>
+      </c>
+      <c r="J216" t="n">
+        <v>0.9888</v>
+      </c>
+      <c r="K216" t="n">
+        <v>1.0682</v>
+      </c>
+      <c r="L216" t="n">
+        <v>1.011</v>
+      </c>
+      <c r="M216" t="n">
+        <v>0.0321</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>building20</t>
+        </is>
+      </c>
+      <c r="B217" t="n">
+        <v>1.2345</v>
+      </c>
+      <c r="C217" t="n">
+        <v>1.2863</v>
+      </c>
+      <c r="D217" t="n">
+        <v>1.2148</v>
+      </c>
+      <c r="E217" t="n">
+        <v>1.2912</v>
+      </c>
+      <c r="F217" t="n">
+        <v>1.2077</v>
+      </c>
+      <c r="G217" t="n">
+        <v>1.2843</v>
+      </c>
+      <c r="H217" t="n">
+        <v>1.2478</v>
+      </c>
+      <c r="I217" t="n">
+        <v>1.2548</v>
+      </c>
+      <c r="J217" t="n">
+        <v>1.2118</v>
+      </c>
+      <c r="K217" t="n">
+        <v>1.1722</v>
+      </c>
+      <c r="L217" t="n">
+        <v>1.2405</v>
+      </c>
+      <c r="M217" t="n">
+        <v>0.0396</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>building3</t>
+        </is>
+      </c>
+      <c r="B218" t="n">
+        <v>0.4488</v>
+      </c>
+      <c r="C218" t="n">
+        <v>0.4532</v>
+      </c>
+      <c r="D218" t="n">
+        <v>0.433</v>
+      </c>
+      <c r="E218" t="n">
+        <v>0.4522</v>
+      </c>
+      <c r="F218" t="n">
+        <v>0.4324</v>
+      </c>
+      <c r="G218" t="n">
+        <v>0.4627</v>
+      </c>
+      <c r="H218" t="n">
+        <v>0.4359</v>
+      </c>
+      <c r="I218" t="n">
+        <v>0.4583</v>
+      </c>
+      <c r="J218" t="n">
+        <v>0.4682</v>
+      </c>
+      <c r="K218" t="n">
+        <v>0.4259</v>
+      </c>
+      <c r="L218" t="n">
+        <v>0.4471</v>
+      </c>
+      <c r="M218" t="n">
+        <v>0.0144</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>building5</t>
+        </is>
+      </c>
+      <c r="B219" t="n">
+        <v>1.5408</v>
+      </c>
+      <c r="C219" t="n">
+        <v>1.6259</v>
+      </c>
+      <c r="D219" t="n">
+        <v>1.5971</v>
+      </c>
+      <c r="E219" t="n">
+        <v>1.5316</v>
+      </c>
+      <c r="F219" t="n">
+        <v>1.5193</v>
+      </c>
+      <c r="G219" t="n">
+        <v>1.6286</v>
+      </c>
+      <c r="H219" t="n">
+        <v>1.5106</v>
+      </c>
+      <c r="I219" t="n">
+        <v>1.5723</v>
+      </c>
+      <c r="J219" t="n">
+        <v>1.6475</v>
+      </c>
+      <c r="K219" t="n">
+        <v>1.4921</v>
+      </c>
+      <c r="L219" t="n">
+        <v>1.5666</v>
+      </c>
+      <c r="M219" t="n">
+        <v>0.0555</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>building6</t>
+        </is>
+      </c>
+      <c r="B220" t="n">
+        <v>0.9073</v>
+      </c>
+      <c r="C220" t="n">
+        <v>0.907</v>
+      </c>
+      <c r="D220" t="n">
+        <v>0.9067</v>
+      </c>
+      <c r="E220" t="n">
+        <v>0.8696</v>
+      </c>
+      <c r="F220" t="n">
+        <v>0.9298</v>
+      </c>
+      <c r="G220" t="n">
+        <v>0.9029</v>
+      </c>
+      <c r="H220" t="n">
+        <v>0.9169</v>
+      </c>
+      <c r="I220" t="n">
+        <v>0.8535</v>
+      </c>
+      <c r="J220" t="n">
+        <v>0.9545</v>
+      </c>
+      <c r="K220" t="n">
+        <v>0.9655</v>
+      </c>
+      <c r="L220" t="n">
+        <v>0.9114</v>
+      </c>
+      <c r="M220" t="n">
+        <v>0.034</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>building8</t>
+        </is>
+      </c>
+      <c r="B221" t="n">
+        <v>0.7266</v>
+      </c>
+      <c r="C221" t="n">
+        <v>0.7905</v>
+      </c>
+      <c r="D221" t="n">
+        <v>0.7611</v>
+      </c>
+      <c r="E221" t="n">
+        <v>0.7818000000000001</v>
+      </c>
+      <c r="F221" t="n">
+        <v>0.7352</v>
+      </c>
+      <c r="G221" t="n">
+        <v>0.7284</v>
+      </c>
+      <c r="H221" t="n">
+        <v>0.7625</v>
+      </c>
+      <c r="I221" t="n">
+        <v>0.7903</v>
+      </c>
+      <c r="J221" t="n">
+        <v>0.7694</v>
+      </c>
+      <c r="K221" t="n">
+        <v>0.7458</v>
+      </c>
+      <c r="L221" t="n">
+        <v>0.7592</v>
+      </c>
+      <c r="M221" t="n">
+        <v>0.0244</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>building9</t>
+        </is>
+      </c>
+      <c r="B222" t="n">
+        <v>0.9913999999999999</v>
+      </c>
+      <c r="C222" t="n">
+        <v>0.9851</v>
+      </c>
+      <c r="D222" t="n">
+        <v>0.9962</v>
+      </c>
+      <c r="E222" t="n">
+        <v>1.0136</v>
+      </c>
+      <c r="F222" t="n">
+        <v>1.0235</v>
+      </c>
+      <c r="G222" t="n">
+        <v>0.9754</v>
+      </c>
+      <c r="H222" t="n">
+        <v>0.9916</v>
+      </c>
+      <c r="I222" t="n">
+        <v>0.9918</v>
+      </c>
+      <c r="J222" t="n">
+        <v>1.0148</v>
+      </c>
+      <c r="K222" t="n">
+        <v>1.0378</v>
+      </c>
+      <c r="L222" t="n">
+        <v>1.0021</v>
+      </c>
+      <c r="M222" t="n">
+        <v>0.0194</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="1" t="inlineStr">
+        <is>
+          <t>r+r — RMSSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="1" t="inlineStr">
+        <is>
+          <t>household</t>
+        </is>
+      </c>
+      <c r="B225" s="1" t="inlineStr">
+        <is>
+          <t>seed0</t>
+        </is>
+      </c>
+      <c r="C225" s="1" t="inlineStr">
+        <is>
+          <t>seed1</t>
+        </is>
+      </c>
+      <c r="D225" s="1" t="inlineStr">
+        <is>
+          <t>seed2</t>
+        </is>
+      </c>
+      <c r="E225" s="1" t="inlineStr">
+        <is>
+          <t>seed3</t>
+        </is>
+      </c>
+      <c r="F225" s="1" t="inlineStr">
+        <is>
+          <t>seed4</t>
+        </is>
+      </c>
+      <c r="G225" s="1" t="inlineStr">
+        <is>
+          <t>seed5</t>
+        </is>
+      </c>
+      <c r="H225" s="1" t="inlineStr">
+        <is>
+          <t>seed6</t>
+        </is>
+      </c>
+      <c r="I225" s="1" t="inlineStr">
+        <is>
+          <t>seed7</t>
+        </is>
+      </c>
+      <c r="J225" s="1" t="inlineStr">
+        <is>
+          <t>seed8</t>
+        </is>
+      </c>
+      <c r="K225" s="1" t="inlineStr">
+        <is>
+          <t>seed9</t>
+        </is>
+      </c>
+      <c r="L225" s="1" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="M225" s="1" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>building11</t>
+        </is>
+      </c>
+      <c r="B226" t="n">
+        <v>0.2945</v>
+      </c>
+      <c r="C226" t="n">
+        <v>0.2994</v>
+      </c>
+      <c r="D226" t="n">
+        <v>0.3014</v>
+      </c>
+      <c r="E226" t="n">
+        <v>0.2949</v>
+      </c>
+      <c r="F226" t="n">
+        <v>0.2877</v>
+      </c>
+      <c r="G226" t="n">
+        <v>0.2833</v>
+      </c>
+      <c r="H226" t="n">
+        <v>0.2899</v>
+      </c>
+      <c r="I226" t="n">
+        <v>0.2915</v>
+      </c>
+      <c r="J226" t="n">
+        <v>0.2718</v>
+      </c>
+      <c r="K226" t="n">
+        <v>0.2771</v>
+      </c>
+      <c r="L226" t="n">
+        <v>0.2891</v>
+      </c>
+      <c r="M226" t="n">
+        <v>0.0095</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>building13</t>
+        </is>
+      </c>
+      <c r="B227" t="n">
+        <v>1.0717</v>
+      </c>
+      <c r="C227" t="n">
+        <v>1.0517</v>
+      </c>
+      <c r="D227" t="n">
+        <v>1.0873</v>
+      </c>
+      <c r="E227" t="n">
+        <v>1.0613</v>
+      </c>
+      <c r="F227" t="n">
+        <v>1.0579</v>
+      </c>
+      <c r="G227" t="n">
+        <v>1.0707</v>
+      </c>
+      <c r="H227" t="n">
+        <v>1.0614</v>
+      </c>
+      <c r="I227" t="n">
+        <v>1.0489</v>
+      </c>
+      <c r="J227" t="n">
+        <v>1.0913</v>
+      </c>
+      <c r="K227" t="n">
+        <v>1.084</v>
+      </c>
+      <c r="L227" t="n">
+        <v>1.0686</v>
+      </c>
+      <c r="M227" t="n">
+        <v>0.015</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>building17</t>
+        </is>
+      </c>
+      <c r="B228" t="n">
+        <v>0.5623</v>
+      </c>
+      <c r="C228" t="n">
+        <v>0.5897</v>
+      </c>
+      <c r="D228" t="n">
+        <v>0.5803</v>
+      </c>
+      <c r="E228" t="n">
+        <v>0.5878</v>
+      </c>
+      <c r="F228" t="n">
+        <v>0.5566</v>
+      </c>
+      <c r="G228" t="n">
+        <v>0.5236</v>
+      </c>
+      <c r="H228" t="n">
+        <v>0.595</v>
+      </c>
+      <c r="I228" t="n">
+        <v>0.5359</v>
+      </c>
+      <c r="J228" t="n">
+        <v>0.5986</v>
+      </c>
+      <c r="K228" t="n">
+        <v>0.5856</v>
+      </c>
+      <c r="L228" t="n">
+        <v>0.5715</v>
+      </c>
+      <c r="M228" t="n">
+        <v>0.0259</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>building19</t>
+        </is>
+      </c>
+      <c r="B229" t="n">
+        <v>0.9529</v>
+      </c>
+      <c r="C229" t="n">
+        <v>0.9641999999999999</v>
+      </c>
+      <c r="D229" t="n">
+        <v>0.974</v>
+      </c>
+      <c r="E229" t="n">
+        <v>0.9282</v>
+      </c>
+      <c r="F229" t="n">
+        <v>0.9874000000000001</v>
+      </c>
+      <c r="G229" t="n">
+        <v>0.9505</v>
+      </c>
+      <c r="H229" t="n">
+        <v>0.9493</v>
+      </c>
+      <c r="I229" t="n">
+        <v>0.9262</v>
+      </c>
+      <c r="J229" t="n">
+        <v>0.9321</v>
+      </c>
+      <c r="K229" t="n">
+        <v>0.9869</v>
+      </c>
+      <c r="L229" t="n">
+        <v>0.9552</v>
+      </c>
+      <c r="M229" t="n">
+        <v>0.0227</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>building20</t>
+        </is>
+      </c>
+      <c r="B230" t="n">
+        <v>1.061</v>
+      </c>
+      <c r="C230" t="n">
+        <v>1.0556</v>
+      </c>
+      <c r="D230" t="n">
+        <v>1.0495</v>
+      </c>
+      <c r="E230" t="n">
+        <v>1.0584</v>
+      </c>
+      <c r="F230" t="n">
+        <v>1.0519</v>
+      </c>
+      <c r="G230" t="n">
+        <v>1.0799</v>
+      </c>
+      <c r="H230" t="n">
+        <v>1.0697</v>
+      </c>
+      <c r="I230" t="n">
+        <v>1.0533</v>
+      </c>
+      <c r="J230" t="n">
+        <v>1.0171</v>
+      </c>
+      <c r="K230" t="n">
+        <v>1.0243</v>
+      </c>
+      <c r="L230" t="n">
+        <v>1.0521</v>
+      </c>
+      <c r="M230" t="n">
+        <v>0.0189</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>building3</t>
+        </is>
+      </c>
+      <c r="B231" t="n">
+        <v>0.4826</v>
+      </c>
+      <c r="C231" t="n">
+        <v>0.4868</v>
+      </c>
+      <c r="D231" t="n">
+        <v>0.4831</v>
+      </c>
+      <c r="E231" t="n">
+        <v>0.4795</v>
+      </c>
+      <c r="F231" t="n">
+        <v>0.4838</v>
+      </c>
+      <c r="G231" t="n">
+        <v>0.4936</v>
+      </c>
+      <c r="H231" t="n">
+        <v>0.4879</v>
+      </c>
+      <c r="I231" t="n">
+        <v>0.4827</v>
+      </c>
+      <c r="J231" t="n">
+        <v>0.4885</v>
+      </c>
+      <c r="K231" t="n">
+        <v>0.4784</v>
+      </c>
+      <c r="L231" t="n">
+        <v>0.4847</v>
+      </c>
+      <c r="M231" t="n">
+        <v>0.0046</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>building5</t>
+        </is>
+      </c>
+      <c r="B232" t="n">
+        <v>1.0997</v>
+      </c>
+      <c r="C232" t="n">
+        <v>1.1226</v>
+      </c>
+      <c r="D232" t="n">
+        <v>1.0819</v>
+      </c>
+      <c r="E232" t="n">
+        <v>1.1017</v>
+      </c>
+      <c r="F232" t="n">
+        <v>1.1052</v>
+      </c>
+      <c r="G232" t="n">
+        <v>1.1079</v>
+      </c>
+      <c r="H232" t="n">
+        <v>1.0807</v>
+      </c>
+      <c r="I232" t="n">
+        <v>1.0959</v>
+      </c>
+      <c r="J232" t="n">
+        <v>1.1433</v>
+      </c>
+      <c r="K232" t="n">
+        <v>1.0773</v>
+      </c>
+      <c r="L232" t="n">
+        <v>1.1016</v>
+      </c>
+      <c r="M232" t="n">
+        <v>0.0202</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>building6</t>
+        </is>
+      </c>
+      <c r="B233" t="n">
+        <v>0.9555</v>
+      </c>
+      <c r="C233" t="n">
+        <v>0.9394</v>
+      </c>
+      <c r="D233" t="n">
+        <v>0.9398</v>
+      </c>
+      <c r="E233" t="n">
+        <v>0.926</v>
+      </c>
+      <c r="F233" t="n">
+        <v>0.9459</v>
+      </c>
+      <c r="G233" t="n">
+        <v>0.9547</v>
+      </c>
+      <c r="H233" t="n">
+        <v>0.9571</v>
+      </c>
+      <c r="I233" t="n">
+        <v>0.9349</v>
+      </c>
+      <c r="J233" t="n">
+        <v>0.9778</v>
+      </c>
+      <c r="K233" t="n">
+        <v>0.9644</v>
+      </c>
+      <c r="L233" t="n">
+        <v>0.9496</v>
+      </c>
+      <c r="M233" t="n">
+        <v>0.0153</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>building8</t>
+        </is>
+      </c>
+      <c r="B234" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="C234" t="n">
+        <v>0.5928</v>
+      </c>
+      <c r="D234" t="n">
+        <v>0.5812</v>
+      </c>
+      <c r="E234" t="n">
+        <v>0.6032</v>
+      </c>
+      <c r="F234" t="n">
+        <v>0.5758</v>
+      </c>
+      <c r="G234" t="n">
+        <v>0.5676</v>
+      </c>
+      <c r="H234" t="n">
+        <v>0.5921999999999999</v>
+      </c>
+      <c r="I234" t="n">
+        <v>0.597</v>
+      </c>
+      <c r="J234" t="n">
+        <v>0.5993000000000001</v>
+      </c>
+      <c r="K234" t="n">
+        <v>0.5648</v>
+      </c>
+      <c r="L234" t="n">
+        <v>0.5854</v>
+      </c>
+      <c r="M234" t="n">
+        <v>0.0135</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>building9</t>
+        </is>
+      </c>
+      <c r="B235" t="n">
         <v>0.9041</v>
       </c>
-      <c r="C209" t="n">
+      <c r="C235" t="n">
         <v>0.9009</v>
       </c>
-      <c r="D209" t="n">
+      <c r="D235" t="n">
         <v>0.8984</v>
       </c>
-      <c r="E209" t="n">
+      <c r="E235" t="n">
         <v>0.9226</v>
       </c>
-      <c r="F209" t="n">
+      <c r="F235" t="n">
         <v>0.896</v>
       </c>
-      <c r="G209" t="n">
+      <c r="G235" t="n">
         <v>0.8855</v>
       </c>
-      <c r="H209" t="n">
+      <c r="H235" t="n">
         <v>0.9079</v>
       </c>
-      <c r="I209" t="n">
+      <c r="I235" t="n">
         <v>0.884</v>
       </c>
-      <c r="J209" t="n">
+      <c r="J235" t="n">
         <v>0.9164</v>
       </c>
-      <c r="K209" t="n">
+      <c r="K235" t="n">
         <v>0.9118000000000001</v>
       </c>
-      <c r="L209" t="n">
+      <c r="L235" t="n">
         <v>0.9028</v>
       </c>
-      <c r="M209" t="n">
+      <c r="M235" t="n">
         <v>0.0125</v>
       </c>
     </row>
@@ -10415,7 +11848,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>training data: synthetic (mUPC): noUPC + mapped UPC (= Ch.5 noSPCP)</t>
+          <t>training data: synthetic (mUPC): noUPC + mapped UPC</t>
         </is>
       </c>
     </row>
@@ -11055,7 +12488,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>experiment: SPCP_DLinear</t>
+          <t>experiment: noSPCP_DLinear</t>
         </is>
       </c>
     </row>
@@ -11069,7 +12502,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>training data: synthetic (SPCP): VA-generated appliance PCPs</t>
+          <t>training data: synthetic (noSPCP): Ch.5 baseline, copied real PCPs + mapped UPC (own simulation)</t>
         </is>
       </c>
     </row>
@@ -11149,16 +12582,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.4623</v>
+        <v>0.4341</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0161</v>
+        <v>0.0276</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3298</v>
+        <v>0.2972</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0101</v>
+        <v>0.0126</v>
       </c>
     </row>
     <row r="14">
@@ -11168,16 +12601,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.0392</v>
+        <v>1.0887</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0273</v>
+        <v>0.0376</v>
       </c>
       <c r="D14" t="n">
-        <v>1.0589</v>
+        <v>1.0858</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0114</v>
+        <v>0.0157</v>
       </c>
     </row>
     <row r="15">
@@ -11187,16 +12620,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.8515</v>
+        <v>0.9025</v>
       </c>
       <c r="C15" t="n">
-        <v>0.06660000000000001</v>
+        <v>0.0356</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5193</v>
+        <v>0.5572</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0296</v>
+        <v>0.0209</v>
       </c>
     </row>
     <row r="16">
@@ -11206,16 +12639,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.023</v>
+        <v>1.0144</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0242</v>
+        <v>0.0187</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9666</v>
+        <v>0.9653</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0225</v>
+        <v>0.0134</v>
       </c>
     </row>
     <row r="17">
@@ -11225,16 +12658,16 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.2549</v>
+        <v>1.2109</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0322</v>
+        <v>0.0398</v>
       </c>
       <c r="D17" t="n">
-        <v>1.1152</v>
+        <v>1.0719</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0337</v>
+        <v>0.0324</v>
       </c>
     </row>
     <row r="18">
@@ -11244,16 +12677,16 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.4802</v>
+        <v>0.4549</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0178</v>
+        <v>0.016</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4994</v>
+        <v>0.4915</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0119</v>
+        <v>0.009599999999999999</v>
       </c>
     </row>
     <row r="19">
@@ -11263,16 +12696,16 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.5784</v>
+        <v>1.5456</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0348</v>
+        <v>0.073</v>
       </c>
       <c r="D19" t="n">
-        <v>1.1166</v>
+        <v>1.0901</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0154</v>
+        <v>0.0357</v>
       </c>
     </row>
     <row r="20">
@@ -11282,16 +12715,16 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9598</v>
+        <v>0.9428</v>
       </c>
       <c r="C20" t="n">
-        <v>0.022</v>
+        <v>0.0146</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9933</v>
+        <v>0.971</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0188</v>
+        <v>0.012</v>
       </c>
     </row>
     <row r="21">
@@ -11301,16 +12734,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.7523</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0613</v>
+        <v>0.0522</v>
       </c>
       <c r="D21" t="n">
-        <v>0.5548999999999999</v>
+        <v>0.5926</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0234</v>
+        <v>0.0211</v>
       </c>
     </row>
     <row r="22">
@@ -11320,16 +12753,16 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.0062</v>
+        <v>1.011</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0326</v>
+        <v>0.0388</v>
       </c>
       <c r="D22" t="n">
-        <v>0.908</v>
+        <v>0.9011</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0103</v>
+        <v>0.0207</v>
       </c>
     </row>
     <row r="23">
@@ -11339,10 +12772,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9349</v>
+        <v>0.9357</v>
       </c>
       <c r="D23" t="n">
-        <v>0.8062</v>
+        <v>0.8024</v>
       </c>
     </row>
     <row r="24">
@@ -11352,10 +12785,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.983</v>
+        <v>0.9769</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9373</v>
+        <v>0.9332</v>
       </c>
     </row>
   </sheetData>
@@ -11382,7 +12815,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>experiment: augmented_DLinear</t>
+          <t>experiment: SPCP_DLinear</t>
         </is>
       </c>
     </row>
@@ -11396,7 +12829,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>training data: augmented: noSPCP + SPCP</t>
+          <t>training data: synthetic (SPCP): VA-generated appliance PCPs</t>
         </is>
       </c>
     </row>
@@ -11476,16 +12909,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.4508</v>
+        <v>0.4389</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0233</v>
+        <v>0.0283</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3065</v>
+        <v>0.2935</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0105</v>
+        <v>0.0119</v>
       </c>
     </row>
     <row r="14">
@@ -11495,16 +12928,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.0533</v>
+        <v>1.048</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0253</v>
+        <v>0.0314</v>
       </c>
       <c r="D14" t="n">
-        <v>1.0667</v>
+        <v>1.0815</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0193</v>
+        <v>0.0146</v>
       </c>
     </row>
     <row r="15">
@@ -11514,16 +12947,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.8762</v>
+        <v>0.9109</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0328</v>
+        <v>0.0475</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5459000000000001</v>
+        <v>0.5602</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0148</v>
+        <v>0.0204</v>
       </c>
     </row>
     <row r="16">
@@ -11533,16 +12966,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.0036</v>
+        <v>1.0124</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0251</v>
+        <v>0.0187</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9526</v>
+        <v>0.9703000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0191</v>
+        <v>0.0119</v>
       </c>
     </row>
     <row r="17">
@@ -11552,16 +12985,16 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.2443</v>
+        <v>1.2367</v>
       </c>
       <c r="C17" t="n">
-        <v>0.035</v>
+        <v>0.0447</v>
       </c>
       <c r="D17" t="n">
-        <v>1.0737</v>
+        <v>1.0861</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0168</v>
+        <v>0.0284</v>
       </c>
     </row>
     <row r="18">
@@ -11571,16 +13004,16 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.4491</v>
+        <v>0.461</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0092</v>
+        <v>0.0126</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4868</v>
+        <v>0.4864</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0043</v>
+        <v>0.008699999999999999</v>
       </c>
     </row>
     <row r="19">
@@ -11590,16 +13023,16 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.5923</v>
+        <v>1.4912</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0606</v>
+        <v>0.0591</v>
       </c>
       <c r="D19" t="n">
-        <v>1.1177</v>
+        <v>1.056</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0268</v>
+        <v>0.0315</v>
       </c>
     </row>
     <row r="20">
@@ -11609,16 +13042,16 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9258</v>
+        <v>0.9224</v>
       </c>
       <c r="C20" t="n">
-        <v>0.023</v>
+        <v>0.0155</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9665</v>
+        <v>0.9616</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0142</v>
+        <v>0.0141</v>
       </c>
     </row>
     <row r="21">
@@ -11628,16 +13061,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7349</v>
+        <v>0.7305</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0528</v>
+        <v>0.057</v>
       </c>
       <c r="D21" t="n">
-        <v>0.5766</v>
+        <v>0.5774</v>
       </c>
       <c r="E21" t="n">
-        <v>0.031</v>
+        <v>0.026</v>
       </c>
     </row>
     <row r="22">
@@ -11647,16 +13080,16 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.9998</v>
+        <v>1.0146</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0267</v>
+        <v>0.0387</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9083</v>
+        <v>0.9039</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0142</v>
+        <v>0.0179</v>
       </c>
     </row>
     <row r="23">
@@ -11666,10 +13099,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.9266</v>
       </c>
       <c r="D23" t="n">
-        <v>0.8001</v>
+        <v>0.7977</v>
       </c>
     </row>
     <row r="24">
@@ -11679,10 +13112,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9628</v>
+        <v>0.9674</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9304</v>
+        <v>0.9327</v>
       </c>
     </row>
   </sheetData>
@@ -11709,7 +13142,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>experiment: r+r_DLinear</t>
+          <t>experiment: augmented_DLinear</t>
         </is>
       </c>
     </row>
@@ -11723,7 +13156,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>training data: r+r: real duplicated (data-volume control)</t>
+          <t>training data: augmented: noSPCP + SPCP</t>
         </is>
       </c>
     </row>
@@ -11803,16 +13236,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.4197</v>
+        <v>0.4279</v>
       </c>
       <c r="C13" t="n">
-        <v>0.021</v>
+        <v>0.0206</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2891</v>
+        <v>0.2898</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0095</v>
+        <v>0.0081</v>
       </c>
     </row>
     <row r="14">
@@ -11822,16 +13255,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.0874</v>
+        <v>1.0647</v>
       </c>
       <c r="C14" t="n">
-        <v>0.024</v>
+        <v>0.0281</v>
       </c>
       <c r="D14" t="n">
-        <v>1.0686</v>
+        <v>1.0675</v>
       </c>
       <c r="E14" t="n">
-        <v>0.015</v>
+        <v>0.0174</v>
       </c>
     </row>
     <row r="15">
@@ -11841,16 +13274,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9426</v>
+        <v>0.9104</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0485</v>
+        <v>0.0424</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5715</v>
+        <v>0.5637</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0259</v>
+        <v>0.0246</v>
       </c>
     </row>
     <row r="16">
@@ -11860,16 +13293,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.011</v>
+        <v>1.0011</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0321</v>
+        <v>0.0293</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9552</v>
+        <v>0.956</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0227</v>
+        <v>0.0196</v>
       </c>
     </row>
     <row r="17">
@@ -11879,16 +13312,16 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.2405</v>
+        <v>1.2432</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0396</v>
+        <v>0.0331</v>
       </c>
       <c r="D17" t="n">
-        <v>1.0521</v>
+        <v>1.0633</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0189</v>
+        <v>0.019</v>
       </c>
     </row>
     <row r="18">
@@ -11898,16 +13331,16 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.4471</v>
+        <v>0.4515</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0144</v>
+        <v>0.015</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4847</v>
+        <v>0.4854</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0046</v>
+        <v>0.0067</v>
       </c>
     </row>
     <row r="19">
@@ -11917,16 +13350,16 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.5666</v>
+        <v>1.5231</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0555</v>
+        <v>0.0522</v>
       </c>
       <c r="D19" t="n">
-        <v>1.1016</v>
+        <v>1.0736</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0202</v>
+        <v>0.0215</v>
       </c>
     </row>
     <row r="20">
@@ -11936,16 +13369,16 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9114</v>
+        <v>0.9115</v>
       </c>
       <c r="C20" t="n">
-        <v>0.034</v>
+        <v>0.0292</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9496</v>
+        <v>0.9569</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0153</v>
+        <v>0.0104</v>
       </c>
     </row>
     <row r="21">
@@ -11955,16 +13388,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7592</v>
+        <v>0.7423</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0244</v>
+        <v>0.0236</v>
       </c>
       <c r="D21" t="n">
-        <v>0.5854</v>
+        <v>0.5764</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0135</v>
+        <v>0.0123</v>
       </c>
     </row>
     <row r="22">
@@ -11974,13 +13407,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.0021</v>
+        <v>1.0142</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0194</v>
+        <v>0.021</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9028</v>
+        <v>0.9086</v>
       </c>
       <c r="E22" t="n">
         <v>0.0125</v>
@@ -11993,10 +13426,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9388</v>
+        <v>0.929</v>
       </c>
       <c r="D23" t="n">
-        <v>0.7961</v>
+        <v>0.7941</v>
       </c>
     </row>
     <row r="24">
@@ -12006,10 +13439,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9724</v>
+        <v>0.9563</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9262</v>
+        <v>0.9323</v>
       </c>
     </row>
   </sheetData>
